--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8ae4082ab43f4c52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0803658adb4b458c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R40999d16d5c34962"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3e7ac942390a4045"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9a354a401e004786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rfbfc89e43a1448bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rbdf69b238fee4513"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3df0d1b0b2504fc7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-07T00:43:44.962Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>ec066f78b134a4ab41e86b94133226ce6f6438520682c580b116eb56ed715fc9</x:v>
+        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>99ba5edfb5f5ec7966456e3ad66285380fe1c91036b9f85ff7846b14c7fd32f2</x:v>
+        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1254,7 +1254,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7102e5642b224c55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R444785f2315140f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1764,7 +1764,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66df920186f24a13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e4430c5e1e4246"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2728,7 +2728,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recb0fd724a06404a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d9722049a2b4bc6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9a354a401e004786"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rfbfc89e43a1448bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rbdf69b238fee4513"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3df0d1b0b2504fc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0087000d867c413e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6a0a775ddcd3470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra029081685f44999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd21c678df0554a9b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -251,7 +251,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-07T12:10:03.268Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
+        <x:v>43d938ca7f8fb8bab04793528cf39b516a7cfa3e6f752cefca7203bfeafa0aac</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
+        <x:v>a162fc27119841a75190b0bc0153cc17495a8bc432ad574a535e8a6799eb9a3d</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1254,7 +1254,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R444785f2315140f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b6e8c32bfd8467b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1543,8 +1543,8 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$42,A7,'Route Points'!$F$7:$F$42)</x:f>
-        <x:v>89.235</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$47,A7,'Route Points'!$F$7:$F$47)</x:f>
+        <x:v>80.6831303111792</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="11" t="str">
@@ -1561,7 +1561,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P7" s="8" t="str">
-        <x:v>Wall bands, wing perimeter containment, entrance wall riser</x:v>
+        <x:v>Wall bands, covered wing-roof crossing, entrance wall riser</x:v>
       </x:c>
       <x:c r="Q7" s="9"/>
       <x:c r="R7" s="9"/>
@@ -1600,7 +1600,7 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$42,A8,'Route Points'!$F$7:$F$42)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$47,A8,'Route Points'!$F$7:$F$47)</x:f>
         <x:v>5.790000000000003</x:v>
       </x:c>
       <x:c r="J8" s="11"/>
@@ -1657,7 +1657,7 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$42,A9,'Route Points'!$F$7:$F$42)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$47,A9,'Route Points'!$F$7:$F$47)</x:f>
         <x:v>2.560000000000007</x:v>
       </x:c>
       <x:c r="J9" s="11"/>
@@ -1714,7 +1714,7 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$42,A10,'Route Points'!$F$7:$F$42)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$47,A10,'Route Points'!$F$7:$F$47)</x:f>
         <x:v>3.4100000000000072</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
@@ -1764,7 +1764,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e4430c5e1e4246"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d933ebd6fe74a29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1941,14 +1941,14 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
         <x:f>SQRT((C10-C9)^2+(D10-D9)^2+(E10-E9)^2)</x:f>
-        <x:v>2.2699999999999996</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
         <x:v>Current</x:v>
@@ -1965,14 +1965,14 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
         <x:f>SQRT((C11-C10)^2+(D11-D10)^2+(E11-E10)^2)</x:f>
-        <x:v>1.3599999999999999</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G11" s="8" t="str">
         <x:v>Current</x:v>
@@ -1986,17 +1986,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
         <x:f>SQRT((C12-C11)^2+(D12-D11)^2+(E12-E11)^2)</x:f>
-        <x:v>4.314999999999998</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G12" s="8" t="str">
         <x:v>Current</x:v>
@@ -2010,17 +2010,17 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>6.26</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
         <x:f>SQRT((C13-C12)^2+(D13-D12)^2+(E13-E12)^2)</x:f>
-        <x:v>2.24</x:v>
+        <x:v>1.9299999999999997</x:v>
       </x:c>
       <x:c r="G13" s="8" t="str">
         <x:v>Current</x:v>
@@ -2034,7 +2034,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>6.26</x:v>
@@ -2044,7 +2044,7 @@
       </x:c>
       <x:c r="F14" s="11" t="n">
         <x:f>SQRT((C14-C13)^2+(D14-D13)^2+(E14-E13)^2)</x:f>
-        <x:v>3.7600000000000002</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G14" s="8" t="str">
         <x:v>Current</x:v>
@@ -2068,7 +2068,7 @@
       </x:c>
       <x:c r="F15" s="11" t="n">
         <x:f>SQRT((C15-C14)^2+(D15-D14)^2+(E15-E14)^2)</x:f>
-        <x:v>8.875</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G15" s="8" t="str">
         <x:v>Current</x:v>
@@ -2085,14 +2085,14 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>6.26</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
         <x:f>SQRT((C16-C15)^2+(D16-D15)^2+(E16-E15)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>0.7800000000000002</x:v>
       </x:c>
       <x:c r="G16" s="8" t="str">
         <x:v>Current</x:v>
@@ -2106,17 +2106,17 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>6.26</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
         <x:f>SQRT((C17-C16)^2+(D17-D16)^2+(E17-E16)^2)</x:f>
-        <x:v>7.199999999999996</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
         <x:v>Current</x:v>
@@ -2130,17 +2130,17 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>6.26</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
         <x:f>SQRT((C18-C17)^2+(D18-D17)^2+(E18-E17)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G18" s="8" t="str">
         <x:v>Current</x:v>
@@ -2154,17 +2154,17 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>6.26</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
         <x:f>SQRT((C19-C18)^2+(D19-D18)^2+(E19-E18)^2)</x:f>
-        <x:v>31.5</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
         <x:v>Current</x:v>
@@ -2178,17 +2178,17 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>6.26</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
         <x:f>SQRT((C20-C19)^2+(D20-D19)^2+(E20-E19)^2)</x:f>
-        <x:v>3.1249999999999996</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
         <x:v>Current</x:v>
@@ -2202,17 +2202,17 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
         <x:f>SQRT((C21-C20)^2+(D21-D20)^2+(E21-E20)^2)</x:f>
-        <x:v>1.3900000000000006</x:v>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G21" s="8" t="str">
         <x:v>Current</x:v>
@@ -2226,17 +2226,17 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
         <x:f>SQRT((C22-C21)^2+(D22-D21)^2+(E22-E21)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G22" s="8" t="str">
         <x:v>Current</x:v>
@@ -2250,17 +2250,17 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>1.5</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
         <x:f>SQRT((C23-C22)^2+(D23-D22)^2+(E23-E22)^2)</x:f>
-        <x:v>6.15</x:v>
+        <x:v>0.7800000000000002</x:v>
       </x:c>
       <x:c r="G23" s="8" t="str">
         <x:v>Current</x:v>
@@ -2274,17 +2274,17 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>5.475</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>1.5</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:f>SQRT((C24-C23)^2+(D24-D23)^2+(E24-E23)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="G24" s="8" t="str">
         <x:v>Current</x:v>
@@ -2292,23 +2292,23 @@
     </x:row>
     <x:row r="25" ht="32" customHeight="1">
       <x:c r="A25" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:DB2</x:v>
       </x:c>
       <x:c r="B25" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C25-C24)^2+(D25-D24)^2+(E25-E24)^2)</x:f>
+        <x:v>3.1249999999999996</x:v>
       </x:c>
       <x:c r="G25" s="8" t="str">
         <x:v>Current</x:v>
@@ -2316,23 +2316,23 @@
     </x:row>
     <x:row r="26" ht="32" customHeight="1">
       <x:c r="A26" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:DB2</x:v>
       </x:c>
       <x:c r="B26" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
         <x:f>SQRT((C26-C25)^2+(D26-D25)^2+(E26-E25)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>1.3900000000000006</x:v>
       </x:c>
       <x:c r="G26" s="8" t="str">
         <x:v>Current</x:v>
@@ -2340,23 +2340,23 @@
     </x:row>
     <x:row r="27" ht="32" customHeight="1">
       <x:c r="A27" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:DB2</x:v>
       </x:c>
       <x:c r="B27" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
         <x:f>SQRT((C27-C26)^2+(D27-D26)^2+(E27-E26)^2)</x:f>
-        <x:v>0.6699999999999999</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G27" s="8" t="str">
         <x:v>Current</x:v>
@@ -2364,23 +2364,23 @@
     </x:row>
     <x:row r="28" ht="32" customHeight="1">
       <x:c r="A28" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:DB2</x:v>
       </x:c>
       <x:c r="B28" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
         <x:f>SQRT((C28-C27)^2+(D28-D27)^2+(E28-E27)^2)</x:f>
-        <x:v>2.95</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="G28" s="8" t="str">
         <x:v>Current</x:v>
@@ -2388,23 +2388,23 @@
     </x:row>
     <x:row r="29" ht="32" customHeight="1">
       <x:c r="A29" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:DB2</x:v>
       </x:c>
       <x:c r="B29" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
         <x:f>SQRT((C29-C28)^2+(D29-D28)^2+(E29-E28)^2)</x:f>
-        <x:v>1.47</x:v>
+        <x:v>0.3799999999999999</x:v>
       </x:c>
       <x:c r="G29" s="8" t="str">
         <x:v>Current</x:v>
@@ -2415,20 +2415,20 @@
         <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B30" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:f>SQRT((C30-C29)^2+(D30-D29)^2+(E30-E29)^2)</x:f>
-        <x:v>0.5399999999999991</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G30" s="8" t="str">
         <x:v>Current</x:v>
@@ -2436,13 +2436,13 @@
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
       <x:c r="A31" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B31" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
         <x:v>1.75</x:v>
@@ -2451,8 +2451,8 @@
         <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C31-C30)^2+(D31-D30)^2+(E31-E30)^2)</x:f>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G31" s="8" t="str">
         <x:v>Current</x:v>
@@ -2460,23 +2460,23 @@
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
       <x:c r="A32" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B32" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
         <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
         <x:f>SQRT((C32-C31)^2+(D32-D31)^2+(E32-E31)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>0.6699999999999999</x:v>
       </x:c>
       <x:c r="G32" s="8" t="str">
         <x:v>Current</x:v>
@@ -2484,10 +2484,10 @@
     </x:row>
     <x:row r="33" ht="32" customHeight="1">
       <x:c r="A33" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B33" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
         <x:v>48.735</x:v>
@@ -2496,11 +2496,11 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:f>SQRT((C33-C32)^2+(D33-D32)^2+(E33-E32)^2)</x:f>
-        <x:v>0.6699999999999999</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="G33" s="8" t="str">
         <x:v>Current</x:v>
@@ -2508,23 +2508,23 @@
     </x:row>
     <x:row r="34" ht="32" customHeight="1">
       <x:c r="A34" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B34" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
         <x:f>SQRT((C34-C33)^2+(D34-D33)^2+(E34-E33)^2)</x:f>
-        <x:v>1</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="G34" s="8" t="str">
         <x:v>Current</x:v>
@@ -2532,23 +2532,23 @@
     </x:row>
     <x:row r="35" ht="32" customHeight="1">
       <x:c r="A35" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B35" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>49.275</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
         <x:f>SQRT((C35-C34)^2+(D35-D34)^2+(E35-E34)^2)</x:f>
-        <x:v>0.5699999999999998</x:v>
+        <x:v>0.5399999999999991</x:v>
       </x:c>
       <x:c r="G35" s="8" t="str">
         <x:v>Current</x:v>
@@ -2559,20 +2559,20 @@
         <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B36" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>48.895</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:f>SQRT((C36-C35)^2+(D36-D35)^2+(E36-E35)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G36" s="8" t="str">
         <x:v>Current</x:v>
@@ -2580,13 +2580,13 @@
     </x:row>
     <x:row r="37" ht="32" customHeight="1">
       <x:c r="A37" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B37" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
         <x:v>1.75</x:v>
@@ -2595,8 +2595,8 @@
         <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C37-C36)^2+(D37-D36)^2+(E37-E36)^2)</x:f>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G37" s="8" t="str">
         <x:v>Current</x:v>
@@ -2604,23 +2604,23 @@
     </x:row>
     <x:row r="38" ht="32" customHeight="1">
       <x:c r="A38" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B38" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
         <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
         <x:f>SQRT((C38-C37)^2+(D38-D37)^2+(E38-E37)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>0.6699999999999999</x:v>
       </x:c>
       <x:c r="G38" s="8" t="str">
         <x:v>Current</x:v>
@@ -2628,10 +2628,10 @@
     </x:row>
     <x:row r="39" ht="32" customHeight="1">
       <x:c r="A39" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B39" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>48.735</x:v>
@@ -2640,11 +2640,11 @@
         <x:v>2.42</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:f>SQRT((C39-C38)^2+(D39-D38)^2+(E39-E38)^2)</x:f>
-        <x:v>0.6699999999999999</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>Current</x:v>
@@ -2652,23 +2652,23 @@
     </x:row>
     <x:row r="40" ht="32" customHeight="1">
       <x:c r="A40" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B40" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:f>SQRT((C40-C39)^2+(D40-D39)^2+(E40-E39)^2)</x:f>
-        <x:v>1.9500000000000002</x:v>
+        <x:v>0.5699999999999998</x:v>
       </x:c>
       <x:c r="G40" s="8" t="str">
         <x:v>Current</x:v>
@@ -2676,23 +2676,23 @@
     </x:row>
     <x:row r="41" ht="32" customHeight="1">
       <x:c r="A41" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B41" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
         <x:f>SQRT((C41-C40)^2+(D41-D40)^2+(E41-E40)^2)</x:f>
-        <x:v>0.47</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G41" s="8" t="str">
         <x:v>Current</x:v>
@@ -2703,32 +2703,152 @@
         <x:v>feeder:FC1</x:v>
       </x:c>
       <x:c r="B42" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>48.895</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="n">
+        <x:v>-1.55</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G42" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="32" customHeight="1">
+      <x:c r="A43" s="8" t="str">
+        <x:v>feeder:FC1</x:v>
+      </x:c>
+      <x:c r="B43" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="n">
+        <x:v>-1.55</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="n">
+        <x:f>SQRT((C43-C42)^2+(D43-D42)^2+(E43-E42)^2)</x:f>
+        <x:v>0.1600000000000037</x:v>
+      </x:c>
+      <x:c r="G43" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="32" customHeight="1">
+      <x:c r="A44" s="8" t="str">
+        <x:v>feeder:FC1</x:v>
+      </x:c>
+      <x:c r="B44" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C44" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="n">
+        <x:v>2.42</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="n">
+        <x:v>-1.55</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="n">
+        <x:f>SQRT((C44-C43)^2+(D44-D43)^2+(E44-E43)^2)</x:f>
+        <x:v>0.6699999999999999</x:v>
+      </x:c>
+      <x:c r="G44" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="32" customHeight="1">
+      <x:c r="A45" s="8" t="str">
+        <x:v>feeder:FC1</x:v>
+      </x:c>
+      <x:c r="B45" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="n">
+        <x:v>2.42</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="n">
+        <x:f>SQRT((C45-C44)^2+(D45-D44)^2+(E45-E44)^2)</x:f>
+        <x:v>1.9500000000000002</x:v>
+      </x:c>
+      <x:c r="G45" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="32" customHeight="1">
+      <x:c r="A46" s="8" t="str">
+        <x:v>feeder:FC1</x:v>
+      </x:c>
+      <x:c r="B46" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C46" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="n">
         <x:v>1.95</x:v>
       </x:c>
-      <x:c r="E42" s="11" t="n">
+      <x:c r="E46" s="11" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="F42" s="11" t="n">
-        <x:f>SQRT((C42-C41)^2+(D42-D41)^2+(E42-E41)^2)</x:f>
+      <x:c r="F46" s="11" t="n">
+        <x:f>SQRT((C46-C45)^2+(D46-D45)^2+(E46-E45)^2)</x:f>
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="G46" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="32" customHeight="1">
+      <x:c r="A47" s="8" t="str">
+        <x:v>feeder:FC1</x:v>
+      </x:c>
+      <x:c r="B47" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="n">
+        <x:f>SQRT((C47-C46)^2+(D47-D46)^2+(E47-E46)^2)</x:f>
         <x:v>0.1600000000000037</x:v>
       </x:c>
-      <x:c r="G42" s="8" t="str">
+      <x:c r="G47" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G42">
+  <x:conditionalFormatting sqref="G7:G47">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d9722049a2b4bc6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83965d2dce2c4527"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0087000d867c413e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6a0a775ddcd3470d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra029081685f44999"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd21c678df0554a9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3e19955754774fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R87384f46306f4dc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6233fd9e15f54991"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R36193586f5524d0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-07T12:10:03.268Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-08T22:16:25.645Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>43d938ca7f8fb8bab04793528cf39b516a7cfa3e6f752cefca7203bfeafa0aac</x:v>
+        <x:v>53ff13ffefd2679cbf8d12a1e21bde566f40af08275ae4f0ff95823f70ea1b77</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>a162fc27119841a75190b0bc0153cc17495a8bc432ad574a535e8a6799eb9a3d</x:v>
+        <x:v>c883a38876b1d2b04788046ec5e1d87651113aa8dbfeb0f5415ba0b829f004ab</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1254,7 +1254,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b6e8c32bfd8467b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc40906389dad4136"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1764,7 +1764,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d933ebd6fe74a29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3e52111f81741d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2848,7 +2848,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83965d2dce2c4527"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd725c76b74a54d73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3e19955754774fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R87384f46306f4dc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6233fd9e15f54991"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R36193586f5524d0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0077ebf232b9449b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rbd89b368a2e64207"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rde540dfdc5c545de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rdfc7f1c6439f4bfb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-08T22:16:25.645Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-09T01:06:21.478Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>53ff13ffefd2679cbf8d12a1e21bde566f40af08275ae4f0ff95823f70ea1b77</x:v>
+        <x:v>d4067e8bb027f3bb435cc6fee67c0fc1d0e462a2d8802a6ada0bb37df793ab52</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>c883a38876b1d2b04788046ec5e1d87651113aa8dbfeb0f5415ba0b829f004ab</x:v>
+        <x:v>e2130aeffb518d934149fa35c32d858856db06e804d9cb98aac4f1896cd3b761</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1254,7 +1254,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc40906389dad4136"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8368e7437e344edc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1764,7 +1764,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3e52111f81741d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb9e64c5d92f421e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2848,7 +2848,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd725c76b74a54d73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83f5f2dff3c94898"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0077ebf232b9449b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rbd89b368a2e64207"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rde540dfdc5c545de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rdfc7f1c6439f4bfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R90c2b5de0f274290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R61738e84b7004568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R487a7a5d952243fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra899faa4e6354002"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-09T01:06:21.478Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>d4067e8bb027f3bb435cc6fee67c0fc1d0e462a2d8802a6ada0bb37df793ab52</x:v>
+        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e2130aeffb518d934149fa35c32d858856db06e804d9cb98aac4f1896cd3b761</x:v>
+        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1254,7 +1254,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8368e7437e344edc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03470f6988d742af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1764,7 +1764,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb9e64c5d92f421e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3978229568ef46ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2848,7 +2848,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83f5f2dff3c94898"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d68da94b3014b9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R90c2b5de0f274290"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R61738e84b7004568"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R487a7a5d952243fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra899faa4e6354002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Raa23de99c93b42ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3b721712a07245d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra1e83c6e1e1f489b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd6bce3e76dc74c8b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="29">
     <x:tableColumn id="1" name="Equipment ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -217,7 +217,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -251,7 +251,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G111" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -495,8 +495,8 @@
         <x:v>Current equipment</x:v>
       </x:c>
       <x:c r="B5" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$11,"Current")</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$17,"Current")</x:f>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -504,8 +504,8 @@
         <x:v>Current routes</x:v>
       </x:c>
       <x:c r="B6" s="16" t="n">
-        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$10,"Current")</x:f>
-        <x:v>4</x:v>
+        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$20,"Current")</x:f>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -513,7 +513,7 @@
         <x:v>Retired equipment / routes</x:v>
       </x:c>
       <x:c r="B7" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$11,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$10,"Retired")</x:f>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$17,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$20,"Retired")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
+        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
+        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -634,7 +634,7 @@
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B22" s="16" t="str">
-        <x:v>DB1, DB2, LC1, FC1 and AV1 enclosures and their shared supply feeders. Shared board sources are cross-references to the distribution-controls register; they are not duplicated here. Architectural fabric stays in the drawing specifications.</x:v>
+        <x:v>DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Shared board sources are cross-references to the distribution-controls register; they are not duplicated here. Architectural fabric stays in the drawing specifications.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="64" customHeight="1">
@@ -951,45 +951,53 @@
     </x:row>
     <x:row r="7" ht="96" customHeight="1">
       <x:c r="A7" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>P-SANCT-B</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
-        <x:v>DB-1 · Main board</x:v>
+        <x:v>Socket · sanctuary side B · axis 10 pier</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
-        <x:v>enclosure</x:v>
+        <x:v>power</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
-      <x:c r="E7" s="8"/>
+      <x:c r="E7" s="8" t="str">
+        <x:v>P1</x:v>
+      </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>43.89</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="I7" s="8" t="str">
-        <x:v>Model enclosure</x:v>
+        <x:v>wall</x:v>
       </x:c>
       <x:c r="J7" s="8" t="str">
         <x:v>Shown</x:v>
       </x:c>
       <x:c r="K7" s="8" t="str">
-        <x:v>n.a.</x:v>
+        <x:v>On</x:v>
       </x:c>
       <x:c r="L7" s="8" t="str">
-        <x:v>200 × 1100 × 800</x:v>
+        <x:v>18 × 86 × 146</x:v>
       </x:c>
       <x:c r="M7" s="8" t="str">
-        <x:v>Service room behind the altar · existing back-wall enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
-      </x:c>
-      <x:c r="N7" s="11"/>
-      <x:c r="O7" s="11"/>
-      <x:c r="P7" s="11"/>
+        <x:v>2 × 16 A 2P+E shuttered · 16 A circuit · 30 mA RCD (provisional) · IP20 indoor · 1656 W planning allowance, not a product load</x:v>
+      </x:c>
+      <x:c r="N7" s="11" t="n">
+        <x:v>1656</x:v>
+      </x:c>
+      <x:c r="O7" s="11" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="P7" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="Q7" s="9"/>
       <x:c r="R7" s="9"/>
       <x:c r="S7" s="9"/>
@@ -1003,50 +1011,62 @@
       <x:c r="AA7" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="AB7" s="8"/>
-      <x:c r="AC7" s="8"/>
+      <x:c r="AB7" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+      </x:c>
+      <x:c r="AC7" s="8" t="str">
+        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: pier face toward the nave, 0.70 m above the side platform and 1.17 m above the wing floor. Surface or casing box; no chase into the structural pier. ENGINEERING HOLD."}</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="96" customHeight="1">
       <x:c r="A8" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>P-NAVE-B</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>DB-2 · Towers &amp; entrance</x:v>
+        <x:v>Socket · mid-nave side B · axis 6</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>enclosure</x:v>
+        <x:v>power</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>DB2</x:v>
-      </x:c>
-      <x:c r="E8" s="8"/>
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str">
+        <x:v>P1</x:v>
+      </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>22.83</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>1.5</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
-        <x:v>Model enclosure</x:v>
+        <x:v>wall</x:v>
       </x:c>
       <x:c r="J8" s="8" t="str">
         <x:v>Shown</x:v>
       </x:c>
       <x:c r="K8" s="8" t="str">
-        <x:v>n.a.</x:v>
+        <x:v>On</x:v>
       </x:c>
       <x:c r="L8" s="8" t="str">
-        <x:v>160 × 620 × 460</x:v>
+        <x:v>18 × 86 × 146</x:v>
       </x:c>
       <x:c r="M8" s="8" t="str">
-        <x:v>Inside the main doors, left of the main door. Procedural enclosure; internal arrangement and hardware pending.</x:v>
-      </x:c>
-      <x:c r="N8" s="11"/>
-      <x:c r="O8" s="11"/>
-      <x:c r="P8" s="11"/>
+        <x:v>2 × 16 A 2P+E shuttered · 16 A circuit · 30 mA RCD (provisional) · IP20 indoor · 1656 W planning allowance, not a product load</x:v>
+      </x:c>
+      <x:c r="N8" s="11" t="n">
+        <x:v>1656</x:v>
+      </x:c>
+      <x:c r="O8" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="P8" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="Q8" s="9"/>
       <x:c r="R8" s="9"/>
       <x:c r="S8" s="9"/>
@@ -1060,50 +1080,62 @@
       <x:c r="AA8" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="AB8" s="8"/>
-      <x:c r="AC8" s="8"/>
+      <x:c r="AB8" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+      </x:c>
+      <x:c r="AC8" s="8" t="str">
+        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: masonry wall between the window and the axis-6 pier, 0.45 m above the nave floor, reached between the bench rows. Not in the structural pier. ENGINEERING HOLD."}</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="96" customHeight="1">
       <x:c r="A9" s="8" t="str">
-        <x:v>LC1</x:v>
+        <x:v>P-TOWER-B</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>LC-1 · Lighting &amp; scene controls</x:v>
+        <x:v>Event power · tower B · inside the porch</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>enclosure</x:v>
+        <x:v>power</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
-        <x:v>DB1</x:v>
-      </x:c>
-      <x:c r="E9" s="8"/>
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="str">
+        <x:v>P3</x:v>
+      </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>-7.85</x:v>
       </x:c>
       <x:c r="I9" s="8" t="str">
-        <x:v>Model enclosure</x:v>
+        <x:v>wall</x:v>
       </x:c>
       <x:c r="J9" s="8" t="str">
         <x:v>Shown</x:v>
       </x:c>
       <x:c r="K9" s="8" t="str">
-        <x:v>n.a.</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="L9" s="8" t="str">
-        <x:v>200 × 900 × 800</x:v>
+        <x:v>221 × 631 × 440</x:v>
       </x:c>
       <x:c r="M9" s="8" t="str">
-        <x:v>Existing service-room lighting enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
-      </x:c>
-      <x:c r="N9" s="11"/>
-      <x:c r="O9" s="11"/>
-      <x:c r="P9" s="11"/>
+        <x:v>1 × 32 A 2P+E industrial + 2 × 16 A · 32 A circuit · 30 mA RCD (provisional) · IP66 lockable (provisional) · 6624 W planning allowance, not a product load</x:v>
+      </x:c>
+      <x:c r="N9" s="11" t="n">
+        <x:v>6624</x:v>
+      </x:c>
+      <x:c r="O9" s="11" t="n">
+        <x:v>-90</x:v>
+      </x:c>
+      <x:c r="P9" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="Q9" s="9"/>
       <x:c r="R9" s="9"/>
       <x:c r="S9" s="9"/>
@@ -1117,50 +1149,62 @@
       <x:c r="AA9" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="AB9" s="8"/>
-      <x:c r="AC9" s="8"/>
+      <x:c r="AB9" s="8" t="str">
+        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="AC9" s="8" t="str">
+        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: inside the tower porch on the front pier, hidden from the front view, 1.3 m above the tower floor. Own 32 A circuit at DB-2, isolated outside events. Supply and feeder size on ENGINEERING HOL"}</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="96" customHeight="1">
       <x:c r="A10" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>P-SANCT-H</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>FC-1 · Fan speed controls</x:v>
+        <x:v>Socket · sanctuary side H · axis 10 pier</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>enclosure</x:v>
+        <x:v>power</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
-      <x:c r="E10" s="8"/>
+      <x:c r="E10" s="8" t="str">
+        <x:v>P2</x:v>
+      </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>43.89</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="I10" s="8" t="str">
-        <x:v>Model enclosure</x:v>
+        <x:v>wall</x:v>
       </x:c>
       <x:c r="J10" s="8" t="str">
         <x:v>Shown</x:v>
       </x:c>
       <x:c r="K10" s="8" t="str">
-        <x:v>n.a.</x:v>
+        <x:v>On</x:v>
       </x:c>
       <x:c r="L10" s="8" t="str">
-        <x:v>200 × 700 × 600</x:v>
+        <x:v>18 × 86 × 146</x:v>
       </x:c>
       <x:c r="M10" s="8" t="str">
-        <x:v>Existing service-room fan enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
-      </x:c>
-      <x:c r="N10" s="11"/>
-      <x:c r="O10" s="11"/>
-      <x:c r="P10" s="11"/>
+        <x:v>2 × 16 A 2P+E shuttered · 16 A circuit · 30 mA RCD (provisional) · IP20 indoor · 1656 W planning allowance, not a product load</x:v>
+      </x:c>
+      <x:c r="N10" s="11" t="n">
+        <x:v>1656</x:v>
+      </x:c>
+      <x:c r="O10" s="11" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="P10" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="Q10" s="9"/>
       <x:c r="R10" s="9"/>
       <x:c r="S10" s="9"/>
@@ -1174,50 +1218,62 @@
       <x:c r="AA10" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="AB10" s="8"/>
-      <x:c r="AC10" s="8"/>
+      <x:c r="AB10" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+      </x:c>
+      <x:c r="AC10" s="8" t="str">
+        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: pier face toward the nave, 0.70 m above the side platform and 1.17 m above the wing floor. Surface or casing box; no chase into the structural pier. ENGINEERING HOLD."}</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="96" customHeight="1">
       <x:c r="A11" s="8" t="str">
-        <x:v>AV1</x:v>
+        <x:v>P-NAVE-H</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>AV-1 · Mixer / amplifier rack</x:v>
+        <x:v>Socket · mid-nave side H · axis 6</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>enclosure</x:v>
+        <x:v>power</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
-      <x:c r="E11" s="8"/>
+      <x:c r="E11" s="8" t="str">
+        <x:v>P2</x:v>
+      </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>22.83</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="H11" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="I11" s="8" t="str">
-        <x:v>Model enclosure</x:v>
+        <x:v>wall</x:v>
       </x:c>
       <x:c r="J11" s="8" t="str">
         <x:v>Shown</x:v>
       </x:c>
       <x:c r="K11" s="8" t="str">
-        <x:v>n.a.</x:v>
+        <x:v>On</x:v>
       </x:c>
       <x:c r="L11" s="8" t="str">
-        <x:v>800 × 1600 × 620</x:v>
+        <x:v>18 × 86 × 146</x:v>
       </x:c>
       <x:c r="M11" s="8" t="str">
-        <x:v>Existing service-room sound rack. Procedural enclosure; internal arrangement and hardware pending.</x:v>
-      </x:c>
-      <x:c r="N11" s="11"/>
-      <x:c r="O11" s="11"/>
-      <x:c r="P11" s="11"/>
+        <x:v>2 × 16 A 2P+E shuttered · 16 A circuit · 30 mA RCD (provisional) · IP20 indoor · 1656 W planning allowance, not a product load</x:v>
+      </x:c>
+      <x:c r="N11" s="11" t="n">
+        <x:v>1656</x:v>
+      </x:c>
+      <x:c r="O11" s="11" t="n">
+        <x:v>-90</x:v>
+      </x:c>
+      <x:c r="P11" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="Q11" s="9"/>
       <x:c r="R11" s="9"/>
       <x:c r="S11" s="9"/>
@@ -1231,30 +1287,388 @@
       <x:c r="AA11" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="AB11" s="8"/>
-      <x:c r="AC11" s="8"/>
+      <x:c r="AB11" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+      </x:c>
+      <x:c r="AC11" s="8" t="str">
+        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: masonry wall between the window and the axis-6 pier, 0.45 m above the nave floor, reached between the bench rows. Not in the structural pier. ENGINEERING HOLD."}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="96" customHeight="1">
+      <x:c r="A12" s="8" t="str">
+        <x:v>P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="str">
+        <x:v>Event power · tower H · inside the porch</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="n">
+        <x:v>7.85</x:v>
+      </x:c>
+      <x:c r="I12" s="8" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="J12" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K12" s="8" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L12" s="8" t="str">
+        <x:v>221 × 631 × 440</x:v>
+      </x:c>
+      <x:c r="M12" s="8" t="str">
+        <x:v>1 × 32 A 2P+E industrial + 2 × 16 A · 32 A circuit · 30 mA RCD (provisional) · IP66 lockable (provisional) · 6624 W planning allowance, not a product load</x:v>
+      </x:c>
+      <x:c r="N12" s="11" t="n">
+        <x:v>6624</x:v>
+      </x:c>
+      <x:c r="O12" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="P12" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="9"/>
+      <x:c r="R12" s="9"/>
+      <x:c r="S12" s="9"/>
+      <x:c r="T12" s="9"/>
+      <x:c r="U12" s="9"/>
+      <x:c r="V12" s="9"/>
+      <x:c r="W12" s="13"/>
+      <x:c r="X12" s="13"/>
+      <x:c r="Y12" s="13"/>
+      <x:c r="Z12" s="9"/>
+      <x:c r="AA12" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB12" s="8" t="str">
+        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="AC12" s="8" t="str">
+        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: inside the tower porch on the front pier, hidden from the front view, 1.3 m above the tower floor. Own 32 A circuit at DB-2, isolated outside events. Supply and feeder size on ENGINEERING HOL"}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="96" customHeight="1">
+      <x:c r="A13" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>DB-1 · Main board</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>enclosure</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E13" s="8"/>
+      <x:c r="F13" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="n">
+        <x:v>-1.55</x:v>
+      </x:c>
+      <x:c r="I13" s="8" t="str">
+        <x:v>Model enclosure</x:v>
+      </x:c>
+      <x:c r="J13" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K13" s="8" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="L13" s="8" t="str">
+        <x:v>200 × 1100 × 800</x:v>
+      </x:c>
+      <x:c r="M13" s="8" t="str">
+        <x:v>Service room behind the altar · existing back-wall enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+      </x:c>
+      <x:c r="N13" s="11"/>
+      <x:c r="O13" s="11"/>
+      <x:c r="P13" s="11"/>
+      <x:c r="Q13" s="9"/>
+      <x:c r="R13" s="9"/>
+      <x:c r="S13" s="9"/>
+      <x:c r="T13" s="9"/>
+      <x:c r="U13" s="9"/>
+      <x:c r="V13" s="9"/>
+      <x:c r="W13" s="13"/>
+      <x:c r="X13" s="13"/>
+      <x:c r="Y13" s="13"/>
+      <x:c r="Z13" s="9"/>
+      <x:c r="AA13" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB13" s="8"/>
+      <x:c r="AC13" s="8"/>
+    </x:row>
+    <x:row r="14" ht="96" customHeight="1">
+      <x:c r="A14" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>DB-2 · Towers &amp; entrance</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>enclosure</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="E14" s="8"/>
+      <x:c r="F14" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="I14" s="8" t="str">
+        <x:v>Model enclosure</x:v>
+      </x:c>
+      <x:c r="J14" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K14" s="8" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="L14" s="8" t="str">
+        <x:v>160 × 620 × 460</x:v>
+      </x:c>
+      <x:c r="M14" s="8" t="str">
+        <x:v>Inside the main doors, left of the main door. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+      </x:c>
+      <x:c r="N14" s="11"/>
+      <x:c r="O14" s="11"/>
+      <x:c r="P14" s="11"/>
+      <x:c r="Q14" s="9"/>
+      <x:c r="R14" s="9"/>
+      <x:c r="S14" s="9"/>
+      <x:c r="T14" s="9"/>
+      <x:c r="U14" s="9"/>
+      <x:c r="V14" s="9"/>
+      <x:c r="W14" s="13"/>
+      <x:c r="X14" s="13"/>
+      <x:c r="Y14" s="13"/>
+      <x:c r="Z14" s="9"/>
+      <x:c r="AA14" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB14" s="8"/>
+      <x:c r="AC14" s="8"/>
+    </x:row>
+    <x:row r="15" ht="96" customHeight="1">
+      <x:c r="A15" s="8" t="str">
+        <x:v>LC1</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>LC-1 · Lighting &amp; scene controls</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>enclosure</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E15" s="8"/>
+      <x:c r="F15" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="n">
+        <x:v>-0.55</x:v>
+      </x:c>
+      <x:c r="I15" s="8" t="str">
+        <x:v>Model enclosure</x:v>
+      </x:c>
+      <x:c r="J15" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K15" s="8" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="L15" s="8" t="str">
+        <x:v>200 × 900 × 800</x:v>
+      </x:c>
+      <x:c r="M15" s="8" t="str">
+        <x:v>Existing service-room lighting enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+      </x:c>
+      <x:c r="N15" s="11"/>
+      <x:c r="O15" s="11"/>
+      <x:c r="P15" s="11"/>
+      <x:c r="Q15" s="9"/>
+      <x:c r="R15" s="9"/>
+      <x:c r="S15" s="9"/>
+      <x:c r="T15" s="9"/>
+      <x:c r="U15" s="9"/>
+      <x:c r="V15" s="9"/>
+      <x:c r="W15" s="13"/>
+      <x:c r="X15" s="13"/>
+      <x:c r="Y15" s="13"/>
+      <x:c r="Z15" s="9"/>
+      <x:c r="AA15" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB15" s="8"/>
+      <x:c r="AC15" s="8"/>
+    </x:row>
+    <x:row r="16" ht="96" customHeight="1">
+      <x:c r="A16" s="8" t="str">
+        <x:v>FC1</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="str">
+        <x:v>FC-1 · Fan speed controls</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="str">
+        <x:v>enclosure</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E16" s="8"/>
+      <x:c r="F16" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="I16" s="8" t="str">
+        <x:v>Model enclosure</x:v>
+      </x:c>
+      <x:c r="J16" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K16" s="8" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="L16" s="8" t="str">
+        <x:v>200 × 700 × 600</x:v>
+      </x:c>
+      <x:c r="M16" s="8" t="str">
+        <x:v>Existing service-room fan enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+      </x:c>
+      <x:c r="N16" s="11"/>
+      <x:c r="O16" s="11"/>
+      <x:c r="P16" s="11"/>
+      <x:c r="Q16" s="9"/>
+      <x:c r="R16" s="9"/>
+      <x:c r="S16" s="9"/>
+      <x:c r="T16" s="9"/>
+      <x:c r="U16" s="9"/>
+      <x:c r="V16" s="9"/>
+      <x:c r="W16" s="13"/>
+      <x:c r="X16" s="13"/>
+      <x:c r="Y16" s="13"/>
+      <x:c r="Z16" s="9"/>
+      <x:c r="AA16" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB16" s="8"/>
+      <x:c r="AC16" s="8"/>
+    </x:row>
+    <x:row r="17" ht="96" customHeight="1">
+      <x:c r="A17" s="8" t="str">
+        <x:v>AV1</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="str">
+        <x:v>AV-1 · Mixer / amplifier rack</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="str">
+        <x:v>enclosure</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E17" s="8"/>
+      <x:c r="F17" s="11" t="n">
+        <x:v>49.275</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="I17" s="8" t="str">
+        <x:v>Model enclosure</x:v>
+      </x:c>
+      <x:c r="J17" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K17" s="8" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="L17" s="8" t="str">
+        <x:v>800 × 1600 × 620</x:v>
+      </x:c>
+      <x:c r="M17" s="8" t="str">
+        <x:v>Existing service-room sound rack. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+      </x:c>
+      <x:c r="N17" s="11"/>
+      <x:c r="O17" s="11"/>
+      <x:c r="P17" s="11"/>
+      <x:c r="Q17" s="9"/>
+      <x:c r="R17" s="9"/>
+      <x:c r="S17" s="9"/>
+      <x:c r="T17" s="9"/>
+      <x:c r="U17" s="9"/>
+      <x:c r="V17" s="9"/>
+      <x:c r="W17" s="13"/>
+      <x:c r="X17" s="13"/>
+      <x:c r="Y17" s="13"/>
+      <x:c r="Z17" s="9"/>
+      <x:c r="AA17" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB17" s="8"/>
+      <x:c r="AC17" s="8"/>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="AA7:AA11">
+  <x:conditionalFormatting sqref="AA7:AA17">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="between" sqref="W7:W11">
+    <x:dataValidation type="decimal" operator="between" sqref="W7:W17">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="X7:X11">
+    <x:dataValidation type="decimal" operator="between" sqref="X7:X17">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y11">
+    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y17">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03470f6988d742af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re79370e2f2dd433a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1543,7 +1957,7 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$47,A7,'Route Points'!$F$7:$F$47)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A7,'Route Points'!$F$7:$F$111)</x:f>
         <x:v>80.6831303111792</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
@@ -1600,7 +2014,7 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$47,A8,'Route Points'!$F$7:$F$47)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A8,'Route Points'!$F$7:$F$111)</x:f>
         <x:v>5.790000000000003</x:v>
       </x:c>
       <x:c r="J8" s="11"/>
@@ -1657,7 +2071,7 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$47,A9,'Route Points'!$F$7:$F$47)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A9,'Route Points'!$F$7:$F$111)</x:f>
         <x:v>2.560000000000007</x:v>
       </x:c>
       <x:c r="J9" s="11"/>
@@ -1714,7 +2128,7 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$47,A10,'Route Points'!$F$7:$F$47)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A10,'Route Points'!$F$7:$F$111)</x:f>
         <x:v>3.4100000000000072</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
@@ -1747,24 +2161,628 @@
       </x:c>
       <x:c r="Z10" s="8"/>
     </x:row>
+    <x:row r="11" ht="90" customHeight="1">
+      <x:c r="A11" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>P1 · B · circuit trunk</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>P-SANCT-B
+P-NAVE-B</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F11" s="8" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H11" s="8" t="str">
+        <x:v>trunk</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A11,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>48.37513031117919</x:v>
+      </x:c>
+      <x:c r="J11" s="11"/>
+      <x:c r="K11" s="11" t="str">
+        <x:f>IF(L11="Full home run",I11+J11,"")</x:f>
+      </x:c>
+      <x:c r="L11" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M11" s="13"/>
+      <x:c r="N11" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M11),L11&lt;&gt;"Shared bundle"),IF(L11="Full home run",K11,I11)+M11,"")</x:f>
+      </x:c>
+      <x:c r="O11" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P11" s="8" t="str">
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+      </x:c>
+      <x:c r="Q11" s="9"/>
+      <x:c r="R11" s="9"/>
+      <x:c r="S11" s="13"/>
+      <x:c r="T11" s="9"/>
+      <x:c r="U11" s="9"/>
+      <x:c r="V11" s="9"/>
+      <x:c r="W11" s="9"/>
+      <x:c r="X11" s="9"/>
+      <x:c r="Y11" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z11" s="8"/>
+    </x:row>
+    <x:row r="12" ht="90" customHeight="1">
+      <x:c r="A12" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="str">
+        <x:v>P1 → Socket · sanctuary side B · axis 10 pier</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="str">
+        <x:v>P-SANCT-B</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F12" s="8" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H12" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A12,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>5.652999999999998</x:v>
+      </x:c>
+      <x:c r="J12" s="11"/>
+      <x:c r="K12" s="11" t="str">
+        <x:f>IF(L12="Full home run",I12+J12,"")</x:f>
+      </x:c>
+      <x:c r="L12" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M12" s="13"/>
+      <x:c r="N12" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M12),L12&lt;&gt;"Shared bundle"),IF(L12="Full home run",K12,I12)+M12,"")</x:f>
+      </x:c>
+      <x:c r="O12" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P12" s="8" t="str">
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+      </x:c>
+      <x:c r="Q12" s="9"/>
+      <x:c r="R12" s="9"/>
+      <x:c r="S12" s="13"/>
+      <x:c r="T12" s="9"/>
+      <x:c r="U12" s="9"/>
+      <x:c r="V12" s="9"/>
+      <x:c r="W12" s="9"/>
+      <x:c r="X12" s="9"/>
+      <x:c r="Y12" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z12" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="90" customHeight="1">
+      <x:c r="A13" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>P1 → Socket · mid-nave side B · axis 6</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="str">
+        <x:v>P-NAVE-B</x:v>
+      </x:c>
+      <x:c r="E13" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F13" s="8" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H13" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A13,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>5.768000000000001</x:v>
+      </x:c>
+      <x:c r="J13" s="11"/>
+      <x:c r="K13" s="11" t="str">
+        <x:f>IF(L13="Full home run",I13+J13,"")</x:f>
+      </x:c>
+      <x:c r="L13" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M13" s="13"/>
+      <x:c r="N13" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M13),L13&lt;&gt;"Shared bundle"),IF(L13="Full home run",K13,I13)+M13,"")</x:f>
+      </x:c>
+      <x:c r="O13" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P13" s="8" t="str">
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+      </x:c>
+      <x:c r="Q13" s="9"/>
+      <x:c r="R13" s="9"/>
+      <x:c r="S13" s="13"/>
+      <x:c r="T13" s="9"/>
+      <x:c r="U13" s="9"/>
+      <x:c r="V13" s="9"/>
+      <x:c r="W13" s="9"/>
+      <x:c r="X13" s="9"/>
+      <x:c r="Y13" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z13" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="90" customHeight="1">
+      <x:c r="A14" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>P3 · B · circuit trunk</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H14" s="8" t="str">
+        <x:v>trunk</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A14,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>8.3</x:v>
+      </x:c>
+      <x:c r="J14" s="11"/>
+      <x:c r="K14" s="11" t="str">
+        <x:f>IF(L14="Full home run",I14+J14,"")</x:f>
+      </x:c>
+      <x:c r="L14" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M14" s="13"/>
+      <x:c r="N14" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M14),L14&lt;&gt;"Shared bundle"),IF(L14="Full home run",K14,I14)+M14,"")</x:f>
+      </x:c>
+      <x:c r="O14" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P14" s="8" t="str">
+        <x:v>Dedicated buried duct from DB-2 below the entrance-hall floor to the tower base; duct, depth, draw pits and water sealing pending.</x:v>
+      </x:c>
+      <x:c r="Q14" s="9"/>
+      <x:c r="R14" s="9"/>
+      <x:c r="S14" s="13"/>
+      <x:c r="T14" s="9"/>
+      <x:c r="U14" s="9"/>
+      <x:c r="V14" s="9"/>
+      <x:c r="W14" s="9"/>
+      <x:c r="X14" s="9"/>
+      <x:c r="Y14" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z14" s="8"/>
+    </x:row>
+    <x:row r="15" ht="90" customHeight="1">
+      <x:c r="A15" s="8" t="str">
+        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>P3 → Event power · tower B · inside the porch</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="F15" s="8" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H15" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A15,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>1.5699999999999994</x:v>
+      </x:c>
+      <x:c r="J15" s="11"/>
+      <x:c r="K15" s="11" t="str">
+        <x:f>IF(L15="Full home run",I15+J15,"")</x:f>
+      </x:c>
+      <x:c r="L15" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M15" s="13"/>
+      <x:c r="N15" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M15),L15&lt;&gt;"Shared bundle"),IF(L15="Full home run",K15,I15)+M15,"")</x:f>
+      </x:c>
+      <x:c r="O15" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P15" s="8" t="str">
+        <x:v>Buried duct below the entrance-hall floor and tower plinth, rising inside the solid tower pier to the cabinet. Duct size, depth, draw pits, water sealing and separation pending; no chase through the arch mouldings.</x:v>
+      </x:c>
+      <x:c r="Q15" s="9"/>
+      <x:c r="R15" s="9"/>
+      <x:c r="S15" s="13"/>
+      <x:c r="T15" s="9"/>
+      <x:c r="U15" s="9"/>
+      <x:c r="V15" s="9"/>
+      <x:c r="W15" s="9"/>
+      <x:c r="X15" s="9"/>
+      <x:c r="Y15" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z15" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="90" customHeight="1">
+      <x:c r="A16" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="str">
+        <x:v>P2 · H · circuit trunk</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="str">
+        <x:v>P-SANCT-H
+P-NAVE-H</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H16" s="8" t="str">
+        <x:v>trunk</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A16,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>54.96713031117919</x:v>
+      </x:c>
+      <x:c r="J16" s="11"/>
+      <x:c r="K16" s="11" t="str">
+        <x:f>IF(L16="Full home run",I16+J16,"")</x:f>
+      </x:c>
+      <x:c r="L16" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M16" s="13"/>
+      <x:c r="N16" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M16),L16&lt;&gt;"Shared bundle"),IF(L16="Full home run",K16,I16)+M16,"")</x:f>
+      </x:c>
+      <x:c r="O16" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P16" s="8" t="str">
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+      </x:c>
+      <x:c r="Q16" s="9"/>
+      <x:c r="R16" s="9"/>
+      <x:c r="S16" s="13"/>
+      <x:c r="T16" s="9"/>
+      <x:c r="U16" s="9"/>
+      <x:c r="V16" s="9"/>
+      <x:c r="W16" s="9"/>
+      <x:c r="X16" s="9"/>
+      <x:c r="Y16" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z16" s="8"/>
+    </x:row>
+    <x:row r="17" ht="90" customHeight="1">
+      <x:c r="A17" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="str">
+        <x:v>P2 → Socket · sanctuary side H · axis 10 pier</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="str">
+        <x:v>P-SANCT-H</x:v>
+      </x:c>
+      <x:c r="E17" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G17" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H17" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A17,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>5.660999999999998</x:v>
+      </x:c>
+      <x:c r="J17" s="11"/>
+      <x:c r="K17" s="11" t="str">
+        <x:f>IF(L17="Full home run",I17+J17,"")</x:f>
+      </x:c>
+      <x:c r="L17" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M17" s="13"/>
+      <x:c r="N17" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M17),L17&lt;&gt;"Shared bundle"),IF(L17="Full home run",K17,I17)+M17,"")</x:f>
+      </x:c>
+      <x:c r="O17" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P17" s="8" t="str">
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+      </x:c>
+      <x:c r="Q17" s="9"/>
+      <x:c r="R17" s="9"/>
+      <x:c r="S17" s="13"/>
+      <x:c r="T17" s="9"/>
+      <x:c r="U17" s="9"/>
+      <x:c r="V17" s="9"/>
+      <x:c r="W17" s="9"/>
+      <x:c r="X17" s="9"/>
+      <x:c r="Y17" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z17" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="90" customHeight="1">
+      <x:c r="A18" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="str">
+        <x:v>P2 → Socket · mid-nave side H · axis 6</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="str">
+        <x:v>P-NAVE-H</x:v>
+      </x:c>
+      <x:c r="E18" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H18" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A18,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>5.776000000000001</x:v>
+      </x:c>
+      <x:c r="J18" s="11"/>
+      <x:c r="K18" s="11" t="str">
+        <x:f>IF(L18="Full home run",I18+J18,"")</x:f>
+      </x:c>
+      <x:c r="L18" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M18" s="13"/>
+      <x:c r="N18" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M18),L18&lt;&gt;"Shared bundle"),IF(L18="Full home run",K18,I18)+M18,"")</x:f>
+      </x:c>
+      <x:c r="O18" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P18" s="8" t="str">
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+      </x:c>
+      <x:c r="Q18" s="9"/>
+      <x:c r="R18" s="9"/>
+      <x:c r="S18" s="13"/>
+      <x:c r="T18" s="9"/>
+      <x:c r="U18" s="9"/>
+      <x:c r="V18" s="9"/>
+      <x:c r="W18" s="9"/>
+      <x:c r="X18" s="9"/>
+      <x:c r="Y18" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z18" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="90" customHeight="1">
+      <x:c r="A19" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="str">
+        <x:v>P4 · H · circuit trunk</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="D19" s="8" t="str">
+        <x:v>P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="E19" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H19" s="8" t="str">
+        <x:v>trunk</x:v>
+      </x:c>
+      <x:c r="I19" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A19,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>14.9</x:v>
+      </x:c>
+      <x:c r="J19" s="11"/>
+      <x:c r="K19" s="11" t="str">
+        <x:f>IF(L19="Full home run",I19+J19,"")</x:f>
+      </x:c>
+      <x:c r="L19" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M19" s="13"/>
+      <x:c r="N19" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M19),L19&lt;&gt;"Shared bundle"),IF(L19="Full home run",K19,I19)+M19,"")</x:f>
+      </x:c>
+      <x:c r="O19" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P19" s="8" t="str">
+        <x:v>Dedicated buried duct from DB-2 below the entrance-hall floor to the tower base; duct, depth, draw pits and water sealing pending.</x:v>
+      </x:c>
+      <x:c r="Q19" s="9"/>
+      <x:c r="R19" s="9"/>
+      <x:c r="S19" s="13"/>
+      <x:c r="T19" s="9"/>
+      <x:c r="U19" s="9"/>
+      <x:c r="V19" s="9"/>
+      <x:c r="W19" s="9"/>
+      <x:c r="X19" s="9"/>
+      <x:c r="Y19" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z19" s="8"/>
+    </x:row>
+    <x:row r="20" ht="90" customHeight="1">
+      <x:c r="A20" s="8" t="str">
+        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B20" s="8" t="str">
+        <x:v>P4 → Event power · tower H · inside the porch</x:v>
+      </x:c>
+      <x:c r="C20" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="D20" s="8" t="str">
+        <x:v>P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="E20" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="F20" s="8" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="G20" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H20" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$111,A20,'Route Points'!$F$7:$F$111)</x:f>
+        <x:v>1.5699999999999994</x:v>
+      </x:c>
+      <x:c r="J20" s="11"/>
+      <x:c r="K20" s="11" t="str">
+        <x:f>IF(L20="Full home run",I20+J20,"")</x:f>
+      </x:c>
+      <x:c r="L20" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M20" s="13"/>
+      <x:c r="N20" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M20),L20&lt;&gt;"Shared bundle"),IF(L20="Full home run",K20,I20)+M20,"")</x:f>
+      </x:c>
+      <x:c r="O20" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P20" s="8" t="str">
+        <x:v>Buried duct below the entrance-hall floor and tower plinth, rising inside the solid tower pier to the cabinet. Duct size, depth, draw pits, water sealing and separation pending; no chase through the arch mouldings.</x:v>
+      </x:c>
+      <x:c r="Q20" s="9"/>
+      <x:c r="R20" s="9"/>
+      <x:c r="S20" s="13"/>
+      <x:c r="T20" s="9"/>
+      <x:c r="U20" s="9"/>
+      <x:c r="V20" s="9"/>
+      <x:c r="W20" s="9"/>
+      <x:c r="X20" s="9"/>
+      <x:c r="Y20" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z20" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="Y7:Y10">
+  <x:conditionalFormatting sqref="Y7:Y20">
     <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M10">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M20">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R10">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R20">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S10">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S20">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3978229568ef46ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65ce2e6e92684416"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2842,13 +3860,1549 @@
         <x:v>Current</x:v>
       </x:c>
     </x:row>
+    <x:row r="48" ht="32" customHeight="1">
+      <x:c r="A48" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B48" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C48" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="D48" s="11" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="E48" s="11" t="n">
+        <x:v>-1.55</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G48" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="32" customHeight="1">
+      <x:c r="A49" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B49" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C49" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="n">
+        <x:v>-1.55</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="n">
+        <x:f>SQRT((C49-C48)^2+(D49-D48)^2+(E49-E48)^2)</x:f>
+        <x:v>0.1600000000000037</x:v>
+      </x:c>
+      <x:c r="G49" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="32" customHeight="1">
+      <x:c r="A50" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B50" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C50" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D50" s="11" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="E50" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F50" s="11" t="n">
+        <x:f>SQRT((C50-C49)^2+(D50-D49)^2+(E50-E49)^2)</x:f>
+        <x:v>0.6900000000000002</x:v>
+      </x:c>
+      <x:c r="G50" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="32" customHeight="1">
+      <x:c r="A51" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B51" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="n">
+        <x:f>SQRT((C51-C50)^2+(D51-D50)^2+(E51-E50)^2)</x:f>
+        <x:v>2.58</x:v>
+      </x:c>
+      <x:c r="G51" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="32" customHeight="1">
+      <x:c r="A52" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B52" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C52" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D52" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E52" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F52" s="11" t="n">
+        <x:f>SQRT((C52-C51)^2+(D52-D51)^2+(E52-E51)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
+      </x:c>
+      <x:c r="G52" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="32" customHeight="1">
+      <x:c r="A53" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B53" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C53" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D53" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E53" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="n">
+        <x:f>SQRT((C53-C52)^2+(D53-D52)^2+(E53-E52)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
+      </x:c>
+      <x:c r="G53" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="32" customHeight="1">
+      <x:c r="A54" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B54" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C54" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D54" s="11" t="n">
+        <x:v>6.1080000000000005</x:v>
+      </x:c>
+      <x:c r="E54" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F54" s="11" t="n">
+        <x:f>SQRT((C54-C53)^2+(D54-D53)^2+(E54-E53)^2)</x:f>
+        <x:v>1.7780000000000005</x:v>
+      </x:c>
+      <x:c r="G54" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="32" customHeight="1">
+      <x:c r="A55" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B55" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C55" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D55" s="11" t="n">
+        <x:v>6.1080000000000005</x:v>
+      </x:c>
+      <x:c r="E55" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F55" s="11" t="n">
+        <x:f>SQRT((C55-C54)^2+(D55-D54)^2+(E55-E54)^2)</x:f>
+        <x:v>4.0600000000000005</x:v>
+      </x:c>
+      <x:c r="G55" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="32" customHeight="1">
+      <x:c r="A56" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B56" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C56" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D56" s="11" t="n">
+        <x:v>6.1080000000000005</x:v>
+      </x:c>
+      <x:c r="E56" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F56" s="11" t="n">
+        <x:f>SQRT((C56-C55)^2+(D56-D55)^2+(E56-E55)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G56" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="32" customHeight="1">
+      <x:c r="A57" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B57" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C57" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D57" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E57" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F57" s="11" t="n">
+        <x:f>SQRT((C57-C56)^2+(D57-D56)^2+(E57-E56)^2)</x:f>
+        <x:v>0.9319999999999995</x:v>
+      </x:c>
+      <x:c r="G57" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="32" customHeight="1">
+      <x:c r="A58" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B58" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C58" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D58" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E58" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F58" s="11" t="n">
+        <x:f>SQRT((C58-C57)^2+(D58-D57)^2+(E58-E57)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G58" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="32" customHeight="1">
+      <x:c r="A59" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B59" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C59" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D59" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E59" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F59" s="11" t="n">
+        <x:f>SQRT((C59-C58)^2+(D59-D58)^2+(E59-E58)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G59" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="32" customHeight="1">
+      <x:c r="A60" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B60" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C60" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D60" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E60" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F60" s="11" t="n">
+        <x:f>SQRT((C60-C59)^2+(D60-D59)^2+(E60-E59)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G60" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="32" customHeight="1">
+      <x:c r="A61" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B61" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C61" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E61" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F61" s="11" t="n">
+        <x:f>SQRT((C61-C60)^2+(D61-D60)^2+(E61-E60)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G61" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="32" customHeight="1">
+      <x:c r="A62" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B62" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C62" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D62" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E62" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F62" s="11" t="n">
+        <x:f>SQRT((C62-C61)^2+(D62-D61)^2+(E62-E61)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G62" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="32" customHeight="1">
+      <x:c r="A63" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B63" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C63" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D63" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E63" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F63" s="11" t="n">
+        <x:f>SQRT((C63-C62)^2+(D63-D62)^2+(E63-E62)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G63" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="32" customHeight="1">
+      <x:c r="A64" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B64" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C64" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D64" s="11" t="n">
+        <x:v>6.1080000000000005</x:v>
+      </x:c>
+      <x:c r="E64" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F64" s="11" t="n">
+        <x:f>SQRT((C64-C63)^2+(D64-D63)^2+(E64-E63)^2)</x:f>
+        <x:v>0.9319999999999995</x:v>
+      </x:c>
+      <x:c r="G64" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="32" customHeight="1">
+      <x:c r="A65" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
+      <x:c r="B65" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C65" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D65" s="11" t="n">
+        <x:v>6.1080000000000005</x:v>
+      </x:c>
+      <x:c r="E65" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F65" s="11" t="n">
+        <x:f>SQRT((C65-C64)^2+(D65-D64)^2+(E65-E64)^2)</x:f>
+        <x:v>14.145000000000003</x:v>
+      </x:c>
+      <x:c r="G65" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="32" customHeight="1">
+      <x:c r="A66" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+      </x:c>
+      <x:c r="B66" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C66" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D66" s="11" t="n">
+        <x:v>6.1080000000000005</x:v>
+      </x:c>
+      <x:c r="E66" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F66" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G66" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="32" customHeight="1">
+      <x:c r="A67" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+      </x:c>
+      <x:c r="B67" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C67" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D67" s="11" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E67" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F67" s="11" t="n">
+        <x:f>SQRT((C67-C66)^2+(D67-D66)^2+(E67-E66)^2)</x:f>
+        <x:v>5.258000000000001</x:v>
+      </x:c>
+      <x:c r="G67" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="32" customHeight="1">
+      <x:c r="A68" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+      </x:c>
+      <x:c r="B68" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C68" s="11" t="n">
+        <x:v>43.89</x:v>
+      </x:c>
+      <x:c r="D68" s="11" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E68" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F68" s="11" t="n">
+        <x:f>SQRT((C68-C67)^2+(D68-D67)^2+(E68-E67)^2)</x:f>
+        <x:v>0.2849999999999966</x:v>
+      </x:c>
+      <x:c r="G68" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="32" customHeight="1">
+      <x:c r="A69" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+      </x:c>
+      <x:c r="B69" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C69" s="11" t="n">
+        <x:v>43.89</x:v>
+      </x:c>
+      <x:c r="D69" s="11" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E69" s="11" t="n">
+        <x:v>-7.25</x:v>
+      </x:c>
+      <x:c r="F69" s="11" t="n">
+        <x:f>SQRT((C69-C68)^2+(D69-D68)^2+(E69-E68)^2)</x:f>
+        <x:v>0.11000000000000032</x:v>
+      </x:c>
+      <x:c r="G69" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="32" customHeight="1">
+      <x:c r="A70" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+      </x:c>
+      <x:c r="B70" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C70" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D70" s="11" t="n">
+        <x:v>6.1080000000000005</x:v>
+      </x:c>
+      <x:c r="E70" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F70" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G70" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="32" customHeight="1">
+      <x:c r="A71" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+      </x:c>
+      <x:c r="B71" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C71" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D71" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="E71" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F71" s="11" t="n">
+        <x:f>SQRT((C71-C70)^2+(D71-D70)^2+(E71-E70)^2)</x:f>
+        <x:v>5.658</x:v>
+      </x:c>
+      <x:c r="G71" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="32" customHeight="1">
+      <x:c r="A72" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+      </x:c>
+      <x:c r="B72" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C72" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D72" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="E72" s="11" t="n">
+        <x:v>-7.25</x:v>
+      </x:c>
+      <x:c r="F72" s="11" t="n">
+        <x:f>SQRT((C72-C71)^2+(D72-D71)^2+(E72-E71)^2)</x:f>
+        <x:v>0.11000000000000032</x:v>
+      </x:c>
+      <x:c r="G72" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="32" customHeight="1">
+      <x:c r="A73" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B73" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C73" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D73" s="11" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E73" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F73" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G73" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="32" customHeight="1">
+      <x:c r="A74" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B74" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C74" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D74" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E74" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F74" s="11" t="n">
+        <x:f>SQRT((C74-C73)^2+(D74-D73)^2+(E74-E73)^2)</x:f>
+        <x:v>1.62</x:v>
+      </x:c>
+      <x:c r="G74" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="32" customHeight="1">
+      <x:c r="A75" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B75" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C75" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D75" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E75" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F75" s="11" t="n">
+        <x:f>SQRT((C75-C74)^2+(D75-D74)^2+(E75-E74)^2)</x:f>
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="G75" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="32" customHeight="1">
+      <x:c r="A76" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B76" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C76" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D76" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E76" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F76" s="11" t="n">
+        <x:f>SQRT((C76-C75)^2+(D76-D75)^2+(E76-E75)^2)</x:f>
+        <x:v>2.28</x:v>
+      </x:c>
+      <x:c r="G76" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="32" customHeight="1">
+      <x:c r="A77" s="8" t="str">
+        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="B77" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C77" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D77" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E77" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F77" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G77" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="32" customHeight="1">
+      <x:c r="A78" s="8" t="str">
+        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="B78" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C78" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D78" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E78" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F78" s="11" t="n">
+        <x:f>SQRT((C78-C77)^2+(D78-D77)^2+(E78-E77)^2)</x:f>
+        <x:v>1.42</x:v>
+      </x:c>
+      <x:c r="G78" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="32" customHeight="1">
+      <x:c r="A79" s="8" t="str">
+        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="B79" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C79" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D79" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E79" s="11" t="n">
+        <x:v>-7.85</x:v>
+      </x:c>
+      <x:c r="F79" s="11" t="n">
+        <x:f>SQRT((C79-C78)^2+(D79-D78)^2+(E79-E78)^2)</x:f>
+        <x:v>0.14999999999999947</x:v>
+      </x:c>
+      <x:c r="G79" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="32" customHeight="1">
+      <x:c r="A80" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B80" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C80" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="D80" s="11" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="E80" s="11" t="n">
+        <x:v>-1.55</x:v>
+      </x:c>
+      <x:c r="F80" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G80" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="32" customHeight="1">
+      <x:c r="A81" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B81" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C81" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D81" s="11" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="E81" s="11" t="n">
+        <x:v>-1.55</x:v>
+      </x:c>
+      <x:c r="F81" s="11" t="n">
+        <x:f>SQRT((C81-C80)^2+(D81-D80)^2+(E81-E80)^2)</x:f>
+        <x:v>0.1600000000000037</x:v>
+      </x:c>
+      <x:c r="G81" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="32" customHeight="1">
+      <x:c r="A82" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B82" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C82" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D82" s="11" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="E82" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F82" s="11" t="n">
+        <x:f>SQRT((C82-C81)^2+(D82-D81)^2+(E82-E81)^2)</x:f>
+        <x:v>0.6900000000000002</x:v>
+      </x:c>
+      <x:c r="G82" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="32" customHeight="1">
+      <x:c r="A83" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B83" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C83" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D83" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E83" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F83" s="11" t="n">
+        <x:f>SQRT((C83-C82)^2+(D83-D82)^2+(E83-E82)^2)</x:f>
+        <x:v>2.58</x:v>
+      </x:c>
+      <x:c r="G83" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="32" customHeight="1">
+      <x:c r="A84" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B84" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C84" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D84" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E84" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F84" s="11" t="n">
+        <x:f>SQRT((C84-C83)^2+(D84-D83)^2+(E84-E83)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
+      </x:c>
+      <x:c r="G84" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="32" customHeight="1">
+      <x:c r="A85" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B85" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C85" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E85" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F85" s="11" t="n">
+        <x:f>SQRT((C85-C84)^2+(D85-D84)^2+(E85-E84)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
+      </x:c>
+      <x:c r="G85" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="32" customHeight="1">
+      <x:c r="A86" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B86" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C86" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D86" s="11" t="n">
+        <x:v>6.1160000000000005</x:v>
+      </x:c>
+      <x:c r="E86" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F86" s="11" t="n">
+        <x:f>SQRT((C86-C85)^2+(D86-D85)^2+(E86-E85)^2)</x:f>
+        <x:v>1.7860000000000005</x:v>
+      </x:c>
+      <x:c r="G86" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="32" customHeight="1">
+      <x:c r="A87" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B87" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C87" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D87" s="11" t="n">
+        <x:v>6.1160000000000005</x:v>
+      </x:c>
+      <x:c r="E87" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F87" s="11" t="n">
+        <x:f>SQRT((C87-C86)^2+(D87-D86)^2+(E87-E86)^2)</x:f>
+        <x:v>10.66</x:v>
+      </x:c>
+      <x:c r="G87" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="32" customHeight="1">
+      <x:c r="A88" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B88" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C88" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D88" s="11" t="n">
+        <x:v>6.1160000000000005</x:v>
+      </x:c>
+      <x:c r="E88" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F88" s="11" t="n">
+        <x:f>SQRT((C88-C87)^2+(D88-D87)^2+(E88-E87)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G88" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="32" customHeight="1">
+      <x:c r="A89" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B89" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C89" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D89" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E89" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F89" s="11" t="n">
+        <x:f>SQRT((C89-C88)^2+(D89-D88)^2+(E89-E88)^2)</x:f>
+        <x:v>0.9239999999999995</x:v>
+      </x:c>
+      <x:c r="G89" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="32" customHeight="1">
+      <x:c r="A90" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B90" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C90" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D90" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E90" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F90" s="11" t="n">
+        <x:f>SQRT((C90-C89)^2+(D90-D89)^2+(E90-E89)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G90" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="32" customHeight="1">
+      <x:c r="A91" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B91" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C91" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D91" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E91" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F91" s="11" t="n">
+        <x:f>SQRT((C91-C90)^2+(D91-D90)^2+(E91-E90)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G91" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="32" customHeight="1">
+      <x:c r="A92" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B92" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C92" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D92" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E92" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F92" s="11" t="n">
+        <x:f>SQRT((C92-C91)^2+(D92-D91)^2+(E92-E91)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G92" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="32" customHeight="1">
+      <x:c r="A93" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B93" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C93" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D93" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E93" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F93" s="11" t="n">
+        <x:f>SQRT((C93-C92)^2+(D93-D92)^2+(E93-E92)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G93" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="32" customHeight="1">
+      <x:c r="A94" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B94" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C94" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D94" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E94" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F94" s="11" t="n">
+        <x:f>SQRT((C94-C93)^2+(D94-D93)^2+(E94-E93)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G94" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="32" customHeight="1">
+      <x:c r="A95" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B95" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C95" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D95" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E95" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F95" s="11" t="n">
+        <x:f>SQRT((C95-C94)^2+(D95-D94)^2+(E95-E94)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G95" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="32" customHeight="1">
+      <x:c r="A96" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B96" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C96" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D96" s="11" t="n">
+        <x:v>6.1160000000000005</x:v>
+      </x:c>
+      <x:c r="E96" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F96" s="11" t="n">
+        <x:f>SQRT((C96-C95)^2+(D96-D95)^2+(E96-E95)^2)</x:f>
+        <x:v>0.9239999999999995</x:v>
+      </x:c>
+      <x:c r="G96" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="32" customHeight="1">
+      <x:c r="A97" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
+      <x:c r="B97" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C97" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D97" s="11" t="n">
+        <x:v>6.1160000000000005</x:v>
+      </x:c>
+      <x:c r="E97" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F97" s="11" t="n">
+        <x:f>SQRT((C97-C96)^2+(D97-D96)^2+(E97-E96)^2)</x:f>
+        <x:v>14.145000000000003</x:v>
+      </x:c>
+      <x:c r="G97" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="32" customHeight="1">
+      <x:c r="A98" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+      </x:c>
+      <x:c r="B98" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C98" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D98" s="11" t="n">
+        <x:v>6.1160000000000005</x:v>
+      </x:c>
+      <x:c r="E98" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F98" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G98" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="32" customHeight="1">
+      <x:c r="A99" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+      </x:c>
+      <x:c r="B99" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C99" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D99" s="11" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E99" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F99" s="11" t="n">
+        <x:f>SQRT((C99-C98)^2+(D99-D98)^2+(E99-E98)^2)</x:f>
+        <x:v>5.266000000000001</x:v>
+      </x:c>
+      <x:c r="G99" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="32" customHeight="1">
+      <x:c r="A100" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+      </x:c>
+      <x:c r="B100" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C100" s="11" t="n">
+        <x:v>43.89</x:v>
+      </x:c>
+      <x:c r="D100" s="11" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E100" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F100" s="11" t="n">
+        <x:f>SQRT((C100-C99)^2+(D100-D99)^2+(E100-E99)^2)</x:f>
+        <x:v>0.2849999999999966</x:v>
+      </x:c>
+      <x:c r="G100" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="32" customHeight="1">
+      <x:c r="A101" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+      </x:c>
+      <x:c r="B101" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C101" s="11" t="n">
+        <x:v>43.89</x:v>
+      </x:c>
+      <x:c r="D101" s="11" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E101" s="11" t="n">
+        <x:v>7.25</x:v>
+      </x:c>
+      <x:c r="F101" s="11" t="n">
+        <x:f>SQRT((C101-C100)^2+(D101-D100)^2+(E101-E100)^2)</x:f>
+        <x:v>0.11000000000000032</x:v>
+      </x:c>
+      <x:c r="G101" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="32" customHeight="1">
+      <x:c r="A102" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+      </x:c>
+      <x:c r="B102" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C102" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D102" s="11" t="n">
+        <x:v>6.1160000000000005</x:v>
+      </x:c>
+      <x:c r="E102" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F102" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G102" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="32" customHeight="1">
+      <x:c r="A103" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+      </x:c>
+      <x:c r="B103" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C103" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D103" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="E103" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F103" s="11" t="n">
+        <x:f>SQRT((C103-C102)^2+(D103-D102)^2+(E103-E102)^2)</x:f>
+        <x:v>5.666</x:v>
+      </x:c>
+      <x:c r="G103" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="32" customHeight="1">
+      <x:c r="A104" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+      </x:c>
+      <x:c r="B104" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C104" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D104" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="E104" s="11" t="n">
+        <x:v>7.25</x:v>
+      </x:c>
+      <x:c r="F104" s="11" t="n">
+        <x:f>SQRT((C104-C103)^2+(D104-D103)^2+(E104-E103)^2)</x:f>
+        <x:v>0.11000000000000032</x:v>
+      </x:c>
+      <x:c r="G104" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="32" customHeight="1">
+      <x:c r="A105" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B105" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C105" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D105" s="11" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E105" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F105" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G105" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="32" customHeight="1">
+      <x:c r="A106" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B106" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C106" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D106" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E106" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F106" s="11" t="n">
+        <x:f>SQRT((C106-C105)^2+(D106-D105)^2+(E106-E105)^2)</x:f>
+        <x:v>1.62</x:v>
+      </x:c>
+      <x:c r="G106" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="32" customHeight="1">
+      <x:c r="A107" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B107" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C107" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D107" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E107" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F107" s="11" t="n">
+        <x:f>SQRT((C107-C106)^2+(D107-D106)^2+(E107-E106)^2)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G107" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="32" customHeight="1">
+      <x:c r="A108" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B108" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C108" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D108" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E108" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F108" s="11" t="n">
+        <x:f>SQRT((C108-C107)^2+(D108-D107)^2+(E108-E107)^2)</x:f>
+        <x:v>2.28</x:v>
+      </x:c>
+      <x:c r="G108" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="32" customHeight="1">
+      <x:c r="A109" s="8" t="str">
+        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B109" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C109" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D109" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E109" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F109" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G109" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="32" customHeight="1">
+      <x:c r="A110" s="8" t="str">
+        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B110" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C110" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D110" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E110" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F110" s="11" t="n">
+        <x:f>SQRT((C110-C109)^2+(D110-D109)^2+(E110-E109)^2)</x:f>
+        <x:v>1.42</x:v>
+      </x:c>
+      <x:c r="G110" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="32" customHeight="1">
+      <x:c r="A111" s="8" t="str">
+        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B111" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C111" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D111" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E111" s="11" t="n">
+        <x:v>7.85</x:v>
+      </x:c>
+      <x:c r="F111" s="11" t="n">
+        <x:f>SQRT((C111-C110)^2+(D111-D110)^2+(E111-E110)^2)</x:f>
+        <x:v>0.14999999999999947</x:v>
+      </x:c>
+      <x:c r="G111" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G47">
+  <x:conditionalFormatting sqref="G7:G111">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d68da94b3014b9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03057cd587cd4f4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Raa23de99c93b42ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3b721712a07245d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra1e83c6e1e1f489b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd6bce3e76dc74c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R55168503ef1d4a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd3295c6d286c4a28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rec0531a4d18f4529"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rffcaf933853f47e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
+        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
+        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1668,7 +1668,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re79370e2f2dd433a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ab0c2bcb92d4ee6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2782,7 +2782,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65ce2e6e92684416"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788949dd1d7a426e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5402,7 +5402,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03057cd587cd4f4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf49ba7a91a3c4c85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R55168503ef1d4a7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd3295c6d286c4a28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rec0531a4d18f4529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rffcaf933853f47e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rbd973130f07e4278"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re862d2d1b91c425d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R15fd3e11c55e4f72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3bf72f3ef7c543fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
+        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -1668,7 +1668,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ab0c2bcb92d4ee6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb94c0d9972c4fa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2782,7 +2782,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788949dd1d7a426e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R095f0558b32a4c47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5402,7 +5402,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf49ba7a91a3c4c85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31cd104656104372"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rbd973130f07e4278"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re862d2d1b91c425d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R15fd3e11c55e4f72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3bf72f3ef7c543fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf30dbcac4a5f4ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R232188058d15480a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0284b8414a204b84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6d019d202eb44165"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -487,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
+        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
+        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1668,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb94c0d9972c4fa6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra27b3be65bbc4755"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2782,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R095f0558b32a4c47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ca0ff8818f64224"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5402,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31cd104656104372"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40943686605f4ff9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf30dbcac4a5f4ef0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R232188058d15480a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0284b8414a204b84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6d019d202eb44165"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3a481f4fe69245a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R5c0c96e3ac544f75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6639ed0f1d754fae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2453cb8479184ef2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
+        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
+        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra27b3be65bbc4755"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95dcdaa2589d4b4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ca0ff8818f64224"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5bb1926c54c4227"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40943686605f4ff9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R471105ac1a3d4c2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3a481f4fe69245a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R5c0c96e3ac544f75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6639ed0f1d754fae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2453cb8479184ef2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb7b0d59a258c4d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1f47c95d95184228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rb1e244cf071d4695"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3fff80b6f3e341a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
+        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
+        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95dcdaa2589d4b4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54a2383f616d4338"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5bb1926c54c4227"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b6debce7b1d4eab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R471105ac1a3d4c2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6665f71e81ba49c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb7b0d59a258c4d3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1f47c95d95184228"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rb1e244cf071d4695"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3fff80b6f3e341a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R325570416c3f4581"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4e6315d72c5948ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0841f87410cf4653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R840e93124e7d4e0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
+        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54a2383f616d4338"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0754d0e00e704439"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b6debce7b1d4eab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R964edd0551f345d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6665f71e81ba49c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8836914809d4a63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R325570416c3f4581"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4e6315d72c5948ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0841f87410cf4653"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R840e93124e7d4e0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb5829182a2074299"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8b669cf53af84028"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6f09b22fb6214cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R56f32136bdc84991"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-19T11:17:33.830Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
+        <x:v>76909d79225afb700a61e3530abc09d363cc6e053b648e6ff87757a6c3bc33f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
+        <x:v>5c2b7909fdbf3eab73054e0a16a6cfe55decd4f3c81b9a88867863ffd7c0fef1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0754d0e00e704439"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90515ca62c8f4fbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R964edd0551f345d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3d739a2e33f4e94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8836914809d4a63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra657177cabde48ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb5829182a2074299"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8b669cf53af84028"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6f09b22fb6214cf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R56f32136bdc84991"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R2530a77f1b664712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra71534e3aac349d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rae1e8b7a8142432b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6f7f09b5c5314295"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-19T11:17:33.830Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-19T13:14:34.808Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>76909d79225afb700a61e3530abc09d363cc6e053b648e6ff87757a6c3bc33f9</x:v>
+        <x:v>5e78147eff2f4a61ae97936ba8b51920b75ba77bd982e40a1cae0206f908332c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>5c2b7909fdbf3eab73054e0a16a6cfe55decd4f3c81b9a88867863ffd7c0fef1</x:v>
+        <x:v>7a659950a4bf89cc57551f6d9714dbafa89ad76ea9820ddefb4bbc73056b5b2e</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90515ca62c8f4fbd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77db2a4e986b432b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3d739a2e33f4e94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R687f39c894204173"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra657177cabde48ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R990c1bae22f54b90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R2530a77f1b664712"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra71534e3aac349d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rae1e8b7a8142432b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6f7f09b5c5314295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf677ea159e844b23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6f2fd49f32c04571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc9488fffe9784bdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0288023c88524a85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-19T13:14:34.808Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5e78147eff2f4a61ae97936ba8b51920b75ba77bd982e40a1cae0206f908332c</x:v>
+        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7a659950a4bf89cc57551f6d9714dbafa89ad76ea9820ddefb4bbc73056b5b2e</x:v>
+        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1021,7 +1021,7 @@
         <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
       </x:c>
       <x:c r="AC7" s="8" t="str">
-        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: pier face toward the nave, 0.70 m above the side platform and 1.17 m above the wing floor. Surface or casing box; no chase into the structural pier. ENGINEERING HOLD."}</x:v>
+        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: pier face toward the nave, 0.69 m above the side platform (+0.16) and 1.17 m above the wing floor. Surface or casing box; no chase into the structural pier. ENGINEERING HOLD."}</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="96" customHeight="1">
@@ -1228,7 +1228,7 @@
         <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
       </x:c>
       <x:c r="AC10" s="8" t="str">
-        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: pier face toward the nave, 0.70 m above the side platform and 1.17 m above the wing floor. Surface or casing box; no chase into the structural pier. ENGINEERING HOLD."}</x:v>
+        <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: pier face toward the nave, 0.69 m above the side platform (+0.16) and 1.17 m above the wing floor. Surface or casing box; no chase into the structural pier. ENGINEERING HOLD."}</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="96" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77db2a4e986b432b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12c22829276648a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R687f39c894204173"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442c820ca2c543e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R990c1bae22f54b90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74cd869e02c646a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rf677ea159e844b23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6f2fd49f32c04571"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc9488fffe9784bdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R0288023c88524a85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3f4c9db087c643a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6c362d9e7ed54795"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf1f6618e2a984f74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rbd0da15446194769"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
+        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
+        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12c22829276648a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c82e47cf6474497"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442c820ca2c543e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b3cb68273df4a20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74cd869e02c646a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39846351c0af4753"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3f4c9db087c643a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6c362d9e7ed54795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rf1f6618e2a984f74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rbd0da15446194769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R84cc5597f04741f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R40ba9cfd061b4ab5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rce3ac98bf56e46f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3cf00d25a2d54ee5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
+        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
+        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c82e47cf6474497"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8130dfbb10f4ee5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b3cb68273df4a20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80c101cd511d48c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39846351c0af4753"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfec61dc917cc4a77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R84cc5597f04741f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R40ba9cfd061b4ab5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rce3ac98bf56e46f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3cf00d25a2d54ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8736127e9636448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6a0ade9927694622"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6aad6ea7cede406b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rddfeaf9d6ead4352"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
+        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
+        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8130dfbb10f4ee5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc05eb13d84e74744"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80c101cd511d48c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc33f1f1ee4684953"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfec61dc917cc4a77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc45fa67938734518"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8736127e9636448c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R6a0ade9927694622"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6aad6ea7cede406b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rddfeaf9d6ead4352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0462e9a4f1f944b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1ce5bb8088094c88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re8287ebb23d54ad4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4de1297f085a4657"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
+        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
+        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc05eb13d84e74744"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54268eee30114633"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc33f1f1ee4684953"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9060d79c897c4f5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc45fa67938734518"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra65d876828e14d30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R0462e9a4f1f944b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1ce5bb8088094c88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re8287ebb23d54ad4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4de1297f085a4657"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R64645df66d034bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R82270f0908724de7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R50463525f1b948a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R64a1b3b45b874ebf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
+        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
+        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54268eee30114633"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32ac150fdb224d58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9060d79c897c4f5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b2886d94a6048b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra65d876828e14d30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4ccfa4408624975"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R64645df66d034bef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R82270f0908724de7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R50463525f1b948a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R64a1b3b45b874ebf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1ab3f92fcde14798"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re60d0f7acff84e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R50d20008cac241ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rdd111d5323f342a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
+        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
+        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1674,7 +1674,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32ac150fdb224d58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3458c3f0dac04ac7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2788,7 +2788,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b2886d94a6048b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a70e8a7b90d4615"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5408,7 +5408,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4ccfa4408624975"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4b1e74726e34007"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1ab3f92fcde14798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re60d0f7acff84e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R50d20008cac241ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rdd111d5323f342a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R54dfc2f01da54f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcc99cbf9c64e48b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R17abe80a8a9c4a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb8bc0581c4fa48b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentRegister" displayName="EquipmentRegister" ref="A6:AC18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="29">
     <x:tableColumn id="1" name="Equipment ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G111" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G129" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -501,8 +501,8 @@
         <x:v>Current equipment</x:v>
       </x:c>
       <x:c r="B5" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$17,"Current")</x:f>
-        <x:v>11</x:v>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$18,"Current")</x:f>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -510,8 +510,8 @@
         <x:v>Current routes</x:v>
       </x:c>
       <x:c r="B6" s="16" t="n">
-        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$20,"Current")</x:f>
-        <x:v>14</x:v>
+        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$25,"Current")</x:f>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -519,8 +519,8 @@
         <x:v>Retired equipment / routes</x:v>
       </x:c>
       <x:c r="B7" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$17,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$20,"Retired")</x:f>
-        <x:v>0</x:v>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$18,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$25,"Retired")</x:f>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
+        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
+        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1156,7 +1156,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB9" s="8" t="str">
-        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+        <x:v>drop:EB1:P3:power:-1:P-TOWER-B</x:v>
       </x:c>
       <x:c r="AC9" s="8" t="str">
         <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: inside the tower porch on the front pier, hidden from the front view, 1.3 m above the tower floor. Own 32 A circuit at DB-2, isolated outside events. Supply and feeder size on ENGINEERING HOL"}</x:v>
@@ -1363,7 +1363,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB12" s="8" t="str">
-        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+        <x:v>drop:EB1:P4:power:1:P-TOWER-H</x:v>
       </x:c>
       <x:c r="AC12" s="8" t="str">
         <x:v>{"loadW":0,"dim":1,"note":"CONCEPT: inside the tower porch on the front pier, hidden from the front view, 1.3 m above the tower floor. Own 32 A circuit at DB-2, isolated outside events. Supply and feeder size on ENGINEERING HOL"}</x:v>
@@ -1441,13 +1441,13 @@
       </x:c>
       <x:c r="E14" s="8"/>
       <x:c r="F14" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="I14" s="8" t="str">
         <x:v>Model enclosure</x:v>
@@ -1462,7 +1462,7 @@
         <x:v>160 × 620 × 460</x:v>
       </x:c>
       <x:c r="M14" s="8" t="str">
-        <x:v>Inside the main doors, left of the main door. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+        <x:v>Ground-floor room of the H-side tower (left on site), inside the closed front wall. Procedural enclosure; internal arrangement and hardware pending.</x:v>
       </x:c>
       <x:c r="N14" s="11"/>
       <x:c r="O14" s="11"/>
@@ -1485,26 +1485,26 @@
     </x:row>
     <x:row r="15" ht="96" customHeight="1">
       <x:c r="A15" s="8" t="str">
-        <x:v>LC1</x:v>
+        <x:v>EB1</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
-        <x:v>LC-1 · Lighting &amp; scene controls</x:v>
+        <x:v>EB-1 · Festival &amp; stage event board</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
         <x:v>enclosure</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="E15" s="8"/>
       <x:c r="F15" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="I15" s="8" t="str">
         <x:v>Model enclosure</x:v>
@@ -1516,10 +1516,10 @@
         <x:v>n.a.</x:v>
       </x:c>
       <x:c r="L15" s="8" t="str">
-        <x:v>200 × 900 × 800</x:v>
+        <x:v>160 × 620 × 460</x:v>
       </x:c>
       <x:c r="M15" s="8" t="str">
-        <x:v>Existing service-room lighting enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+        <x:v>Ground-floor room of the H-side tower, beside DB-2. Procedural enclosure; internal arrangement and hardware pending.</x:v>
       </x:c>
       <x:c r="N15" s="11"/>
       <x:c r="O15" s="11"/>
@@ -1542,10 +1542,10 @@
     </x:row>
     <x:row r="16" ht="96" customHeight="1">
       <x:c r="A16" s="8" t="str">
-        <x:v>FC1</x:v>
+        <x:v>LC1</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
-        <x:v>FC-1 · Fan speed controls</x:v>
+        <x:v>LC-1 · Lighting &amp; scene controls</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
         <x:v>enclosure</x:v>
@@ -1558,10 +1558,10 @@
         <x:v>48.895</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="I16" s="8" t="str">
         <x:v>Model enclosure</x:v>
@@ -1573,10 +1573,10 @@
         <x:v>n.a.</x:v>
       </x:c>
       <x:c r="L16" s="8" t="str">
-        <x:v>200 × 700 × 600</x:v>
+        <x:v>200 × 900 × 800</x:v>
       </x:c>
       <x:c r="M16" s="8" t="str">
-        <x:v>Existing service-room fan enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+        <x:v>Existing service-room lighting enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
       </x:c>
       <x:c r="N16" s="11"/>
       <x:c r="O16" s="11"/>
@@ -1599,10 +1599,10 @@
     </x:row>
     <x:row r="17" ht="96" customHeight="1">
       <x:c r="A17" s="8" t="str">
-        <x:v>AV1</x:v>
+        <x:v>FC1</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
-        <x:v>AV-1 · Mixer / amplifier rack</x:v>
+        <x:v>FC-1 · Fan speed controls</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
         <x:v>enclosure</x:v>
@@ -1612,13 +1612,13 @@
       </x:c>
       <x:c r="E17" s="8"/>
       <x:c r="F17" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I17" s="8" t="str">
         <x:v>Model enclosure</x:v>
@@ -1630,10 +1630,10 @@
         <x:v>n.a.</x:v>
       </x:c>
       <x:c r="L17" s="8" t="str">
-        <x:v>800 × 1600 × 620</x:v>
+        <x:v>200 × 700 × 600</x:v>
       </x:c>
       <x:c r="M17" s="8" t="str">
-        <x:v>Existing service-room sound rack. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+        <x:v>Existing service-room fan enclosure. Procedural enclosure; internal arrangement and hardware pending.</x:v>
       </x:c>
       <x:c r="N17" s="11"/>
       <x:c r="O17" s="11"/>
@@ -1654,27 +1654,84 @@
       <x:c r="AB17" s="8"/>
       <x:c r="AC17" s="8"/>
     </x:row>
+    <x:row r="18" ht="96" customHeight="1">
+      <x:c r="A18" s="8" t="str">
+        <x:v>AV1</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="str">
+        <x:v>AV-1 · Mixer / amplifier rack</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="str">
+        <x:v>enclosure</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="E18" s="8"/>
+      <x:c r="F18" s="11" t="n">
+        <x:v>49.275</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="I18" s="8" t="str">
+        <x:v>Model enclosure</x:v>
+      </x:c>
+      <x:c r="J18" s="8" t="str">
+        <x:v>Shown</x:v>
+      </x:c>
+      <x:c r="K18" s="8" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="L18" s="8" t="str">
+        <x:v>800 × 1600 × 620</x:v>
+      </x:c>
+      <x:c r="M18" s="8" t="str">
+        <x:v>Existing service-room sound rack. Procedural enclosure; internal arrangement and hardware pending.</x:v>
+      </x:c>
+      <x:c r="N18" s="11"/>
+      <x:c r="O18" s="11"/>
+      <x:c r="P18" s="11"/>
+      <x:c r="Q18" s="9"/>
+      <x:c r="R18" s="9"/>
+      <x:c r="S18" s="9"/>
+      <x:c r="T18" s="9"/>
+      <x:c r="U18" s="9"/>
+      <x:c r="V18" s="9"/>
+      <x:c r="W18" s="13"/>
+      <x:c r="X18" s="13"/>
+      <x:c r="Y18" s="13"/>
+      <x:c r="Z18" s="9"/>
+      <x:c r="AA18" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="AB18" s="8"/>
+      <x:c r="AC18" s="8"/>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="AA7:AA17">
+  <x:conditionalFormatting sqref="AA7:AA18">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="between" sqref="W7:W17">
+    <x:dataValidation type="decimal" operator="between" sqref="W7:W18">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="X7:X17">
+    <x:dataValidation type="decimal" operator="between" sqref="X7:X18">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y17">
+    <x:dataValidation type="decimal" operator="between" sqref="Y7:Y18">
       <x:formula1>-1000</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3458c3f0dac04ac7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R328662b1a11846b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1963,8 +2020,8 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A7,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>80.6831303111792</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A7,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>94.9631303111792</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="11" t="str">
@@ -1998,20 +2055,20 @@
     </x:row>
     <x:row r="8" ht="90" customHeight="1">
       <x:c r="A8" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:EB1</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>DB-1 → AV1 equipment supply</x:v>
+        <x:v>DB-2 → EB-1 event board supply</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str"/>
       <x:c r="E8" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>AV1-SUPPLY</x:v>
+        <x:v>EB1-SUPPLY</x:v>
       </x:c>
       <x:c r="G8" s="8" t="str">
         <x:v>feeder</x:v>
@@ -2020,8 +2077,8 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A8,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>5.790000000000003</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A8,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="J8" s="11"/>
       <x:c r="K8" s="11" t="str">
@@ -2038,7 +2095,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P8" s="8" t="str">
-        <x:v>Existing service-room wall tray / local equipment connection</x:v>
+        <x:v>Short tray between the two boards on the tower front wall</x:v>
       </x:c>
       <x:c r="Q8" s="9"/>
       <x:c r="R8" s="9"/>
@@ -2055,10 +2112,10 @@
     </x:row>
     <x:row r="9" ht="90" customHeight="1">
       <x:c r="A9" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>DB-1 → LC1 equipment supply</x:v>
+        <x:v>DB-1 → AV1 equipment supply</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
         <x:v>DB1</x:v>
@@ -2068,7 +2125,7 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>LC1-SUPPLY</x:v>
+        <x:v>AV1-SUPPLY</x:v>
       </x:c>
       <x:c r="G9" s="8" t="str">
         <x:v>feeder</x:v>
@@ -2077,8 +2134,8 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A9,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>2.560000000000007</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A9,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>5.790000000000003</x:v>
       </x:c>
       <x:c r="J9" s="11"/>
       <x:c r="K9" s="11" t="str">
@@ -2112,10 +2169,10 @@
     </x:row>
     <x:row r="10" ht="90" customHeight="1">
       <x:c r="A10" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>DB-1 → FC1 equipment supply</x:v>
+        <x:v>DB-1 → LC1 equipment supply</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
         <x:v>DB1</x:v>
@@ -2125,7 +2182,7 @@
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>FC1-SUPPLY</x:v>
+        <x:v>LC1-SUPPLY</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
         <x:v>feeder</x:v>
@@ -2134,8 +2191,8 @@
         <x:v>feeder</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A10,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>3.4100000000000072</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A10,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>2.560000000000007</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
       <x:c r="K10" s="11" t="str">
@@ -2169,33 +2226,30 @@
     </x:row>
     <x:row r="11" ht="90" customHeight="1">
       <x:c r="A11" s="8" t="str">
-        <x:v>trunk:DB1:P1:power:-1</x:v>
+        <x:v>feeder:FC1</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>P1 · B · circuit trunk</x:v>
+        <x:v>DB-1 → FC1 equipment supply</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
-      <x:c r="D11" s="8" t="str">
-        <x:v>P-SANCT-B
-P-NAVE-B</x:v>
-      </x:c>
+      <x:c r="D11" s="8" t="str"/>
       <x:c r="E11" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>P1</x:v>
+        <x:v>FC1-SUPPLY</x:v>
       </x:c>
       <x:c r="G11" s="8" t="str">
-        <x:v>power</x:v>
+        <x:v>feeder</x:v>
       </x:c>
       <x:c r="H11" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>feeder</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A11,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>48.37513031117919</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A11,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>3.4100000000000072</x:v>
       </x:c>
       <x:c r="J11" s="11"/>
       <x:c r="K11" s="11" t="str">
@@ -2212,7 +2266,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P11" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Existing service-room wall tray / local equipment connection</x:v>
       </x:c>
       <x:c r="Q11" s="9"/>
       <x:c r="R11" s="9"/>
@@ -2229,16 +2283,17 @@
     </x:row>
     <x:row r="12" ht="90" customHeight="1">
       <x:c r="A12" s="8" t="str">
-        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+        <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>P1 → Socket · sanctuary side B · axis 10 pier</x:v>
+        <x:v>P1 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
-        <x:v>P-SANCT-B</x:v>
+        <x:v>P-SANCT-B
+P-NAVE-B</x:v>
       </x:c>
       <x:c r="E12" s="8" t="str">
         <x:v>DB1</x:v>
@@ -2250,11 +2305,11 @@
         <x:v>power</x:v>
       </x:c>
       <x:c r="H12" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A12,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>5.652999999999998</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A12,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>48.37513031117919</x:v>
       </x:c>
       <x:c r="J12" s="11"/>
       <x:c r="K12" s="11" t="str">
@@ -2271,7 +2326,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P12" s="8" t="str">
-        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q12" s="9"/>
       <x:c r="R12" s="9"/>
@@ -2284,22 +2339,20 @@
       <x:c r="Y12" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z12" s="8" t="str">
-        <x:v>trunk:DB1:P1:power:-1</x:v>
-      </x:c>
+      <x:c r="Z12" s="8"/>
     </x:row>
     <x:row r="13" ht="90" customHeight="1">
       <x:c r="A13" s="8" t="str">
-        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
-        <x:v>P1 → Socket · mid-nave side B · axis 6</x:v>
+        <x:v>P1 → Socket · sanctuary side B · axis 10 pier</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
-        <x:v>P-NAVE-B</x:v>
+        <x:v>P-SANCT-B</x:v>
       </x:c>
       <x:c r="E13" s="8" t="str">
         <x:v>DB1</x:v>
@@ -2314,8 +2367,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A13,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>5.768000000000001</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A13,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>5.652999999999998</x:v>
       </x:c>
       <x:c r="J13" s="11"/>
       <x:c r="K13" s="11" t="str">
@@ -2351,32 +2404,32 @@
     </x:row>
     <x:row r="14" ht="90" customHeight="1">
       <x:c r="A14" s="8" t="str">
-        <x:v>trunk:DB2:P3:power:-1</x:v>
+        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
-        <x:v>P3 · B · circuit trunk</x:v>
+        <x:v>P1 → Socket · mid-nave side B · axis 6</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
-        <x:v>P-TOWER-B</x:v>
+        <x:v>P-NAVE-B</x:v>
       </x:c>
       <x:c r="E14" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>P3</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G14" s="8" t="str">
         <x:v>power</x:v>
       </x:c>
       <x:c r="H14" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A14,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>8.3</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A14,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>5.768000000000001</x:v>
       </x:c>
       <x:c r="J14" s="11"/>
       <x:c r="K14" s="11" t="str">
@@ -2393,7 +2446,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P14" s="8" t="str">
-        <x:v>Dedicated buried duct from DB-2 below the entrance-hall floor to the tower base; duct, depth, draw pits and water sealing pending.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q14" s="9"/>
       <x:c r="R14" s="9"/>
@@ -2406,17 +2459,19 @@
       <x:c r="Y14" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z14" s="8"/>
+      <x:c r="Z14" s="8" t="str">
+        <x:v>trunk:DB1:P1:power:-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="90" customHeight="1">
       <x:c r="A15" s="8" t="str">
-        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+        <x:v>trunk:EB1:P3:power:-1</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
-        <x:v>P3 → Event power · tower B · inside the porch</x:v>
+        <x:v>P3 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>EB1</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>P-TOWER-B</x:v>
@@ -2431,11 +2486,11 @@
         <x:v>power</x:v>
       </x:c>
       <x:c r="H15" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A15,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>1.5699999999999994</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A15,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>20.28</x:v>
       </x:c>
       <x:c r="J15" s="11"/>
       <x:c r="K15" s="11" t="str">
@@ -2452,7 +2507,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P15" s="8" t="str">
-        <x:v>Buried duct below the entrance-hall floor and tower plinth, rising inside the solid tower pier to the cabinet. Duct size, depth, draw pits, water sealing and separation pending; no chase through the arch mouldings.</x:v>
+        <x:v>Dedicated buried duct from EB-1 (beside DB-2) below the entrance-hall floor to the tower base; duct, depth, draw pits and water sealing pending.</x:v>
       </x:c>
       <x:c r="Q15" s="9"/>
       <x:c r="R15" s="9"/>
@@ -2465,39 +2520,36 @@
       <x:c r="Y15" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z15" s="8" t="str">
-        <x:v>trunk:DB2:P3:power:-1</x:v>
-      </x:c>
+      <x:c r="Z15" s="8"/>
     </x:row>
     <x:row r="16" ht="90" customHeight="1">
       <x:c r="A16" s="8" t="str">
-        <x:v>trunk:DB1:P2:power:1</x:v>
+        <x:v>drop:EB1:P3:power:-1:P-TOWER-B</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
-        <x:v>P2 · H · circuit trunk</x:v>
+        <x:v>P3 → Event power · tower B · inside the porch</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>EB1</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
-        <x:v>P-SANCT-H
-P-NAVE-H</x:v>
+        <x:v>P-TOWER-B</x:v>
       </x:c>
       <x:c r="E16" s="8" t="str">
-        <x:v>DB1</x:v>
+        <x:v>DB2</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>P2</x:v>
+        <x:v>P3</x:v>
       </x:c>
       <x:c r="G16" s="8" t="str">
         <x:v>power</x:v>
       </x:c>
       <x:c r="H16" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A16,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>54.96713031117919</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A16,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>1.5699999999999994</x:v>
       </x:c>
       <x:c r="J16" s="11"/>
       <x:c r="K16" s="11" t="str">
@@ -2514,7 +2566,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P16" s="8" t="str">
-        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+        <x:v>Buried duct below the entrance-hall floor and tower plinth, rising inside the solid tower pier to the cabinet. Duct size, depth, draw pits, water sealing and separation pending; no chase through the arch mouldings.</x:v>
       </x:c>
       <x:c r="Q16" s="9"/>
       <x:c r="R16" s="9"/>
@@ -2527,20 +2579,23 @@
       <x:c r="Y16" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z16" s="8"/>
+      <x:c r="Z16" s="8" t="str">
+        <x:v>trunk:EB1:P3:power:-1</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="90" customHeight="1">
       <x:c r="A17" s="8" t="str">
-        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+        <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
-        <x:v>P2 → Socket · sanctuary side H · axis 10 pier</x:v>
+        <x:v>P2 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
-        <x:v>P-SANCT-H</x:v>
+        <x:v>P-SANCT-H
+P-NAVE-H</x:v>
       </x:c>
       <x:c r="E17" s="8" t="str">
         <x:v>DB1</x:v>
@@ -2552,11 +2607,11 @@
         <x:v>power</x:v>
       </x:c>
       <x:c r="H17" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A17,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>5.660999999999998</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A17,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>54.96713031117919</x:v>
       </x:c>
       <x:c r="J17" s="11"/>
       <x:c r="K17" s="11" t="str">
@@ -2573,7 +2628,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P17" s="8" t="str">
-        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q17" s="9"/>
       <x:c r="R17" s="9"/>
@@ -2586,22 +2641,20 @@
       <x:c r="Y17" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z17" s="8" t="str">
-        <x:v>trunk:DB1:P2:power:1</x:v>
-      </x:c>
+      <x:c r="Z17" s="8"/>
     </x:row>
     <x:row r="18" ht="90" customHeight="1">
       <x:c r="A18" s="8" t="str">
-        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
       </x:c>
       <x:c r="B18" s="8" t="str">
-        <x:v>P2 → Socket · mid-nave side H · axis 6</x:v>
+        <x:v>P2 → Socket · sanctuary side H · axis 10 pier</x:v>
       </x:c>
       <x:c r="C18" s="8" t="str">
         <x:v>DB1</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str">
-        <x:v>P-NAVE-H</x:v>
+        <x:v>P-SANCT-H</x:v>
       </x:c>
       <x:c r="E18" s="8" t="str">
         <x:v>DB1</x:v>
@@ -2616,8 +2669,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A18,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>5.776000000000001</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A18,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>5.660999999999998</x:v>
       </x:c>
       <x:c r="J18" s="11"/>
       <x:c r="K18" s="11" t="str">
@@ -2653,32 +2706,32 @@
     </x:row>
     <x:row r="19" ht="90" customHeight="1">
       <x:c r="A19" s="8" t="str">
-        <x:v>trunk:DB2:P4:power:1</x:v>
+        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
-        <x:v>P4 · H · circuit trunk</x:v>
+        <x:v>P2 → Socket · mid-nave side H · axis 6</x:v>
       </x:c>
       <x:c r="C19" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
-        <x:v>P-TOWER-H</x:v>
+        <x:v>P-NAVE-H</x:v>
       </x:c>
       <x:c r="E19" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>P4</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
         <x:v>power</x:v>
       </x:c>
       <x:c r="H19" s="8" t="str">
-        <x:v>trunk</x:v>
+        <x:v>drop</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A19,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>14.9</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A19,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>5.776000000000001</x:v>
       </x:c>
       <x:c r="J19" s="11"/>
       <x:c r="K19" s="11" t="str">
@@ -2695,7 +2748,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P19" s="8" t="str">
-        <x:v>Dedicated buried duct from DB-2 below the entrance-hall floor to the tower base; duct, depth, draw pits and water sealing pending.</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q19" s="9"/>
       <x:c r="R19" s="9"/>
@@ -2708,17 +2761,19 @@
       <x:c r="Y19" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z19" s="8"/>
+      <x:c r="Z19" s="8" t="str">
+        <x:v>trunk:DB1:P2:power:1</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="90" customHeight="1">
       <x:c r="A20" s="8" t="str">
-        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+        <x:v>trunk:EB1:P4:power:1</x:v>
       </x:c>
       <x:c r="B20" s="8" t="str">
-        <x:v>P4 → Event power · tower H · inside the porch</x:v>
+        <x:v>P4 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C20" s="8" t="str">
-        <x:v>DB2</x:v>
+        <x:v>EB1</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>P-TOWER-H</x:v>
@@ -2733,11 +2788,11 @@
         <x:v>power</x:v>
       </x:c>
       <x:c r="H20" s="8" t="str">
-        <x:v>drop</x:v>
+        <x:v>trunk</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$111,A20,'Route Points'!$F$7:$F$111)</x:f>
-        <x:v>1.5699999999999994</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A20,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>4.88</x:v>
       </x:c>
       <x:c r="J20" s="11"/>
       <x:c r="K20" s="11" t="str">
@@ -2754,7 +2809,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P20" s="8" t="str">
-        <x:v>Buried duct below the entrance-hall floor and tower plinth, rising inside the solid tower pier to the cabinet. Duct size, depth, draw pits, water sealing and separation pending; no chase through the arch mouldings.</x:v>
+        <x:v>Dedicated buried duct from EB-1 (beside DB-2) below the entrance-hall floor to the tower base; duct, depth, draw pits and water sealing pending.</x:v>
       </x:c>
       <x:c r="Q20" s="9"/>
       <x:c r="R20" s="9"/>
@@ -2767,28 +2822,327 @@
       <x:c r="Y20" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
-      <x:c r="Z20" s="8" t="str">
+      <x:c r="Z20" s="8"/>
+    </x:row>
+    <x:row r="21" ht="90" customHeight="1">
+      <x:c r="A21" s="8" t="str">
+        <x:v>drop:EB1:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="str">
+        <x:v>P4 → Event power · tower H · inside the porch</x:v>
+      </x:c>
+      <x:c r="C21" s="8" t="str">
+        <x:v>EB1</x:v>
+      </x:c>
+      <x:c r="D21" s="8" t="str">
+        <x:v>P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="E21" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="F21" s="8" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="G21" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H21" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A21,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>1.5699999999999994</x:v>
+      </x:c>
+      <x:c r="J21" s="11"/>
+      <x:c r="K21" s="11" t="str">
+        <x:f>IF(L21="Full home run",I21+J21,"")</x:f>
+      </x:c>
+      <x:c r="L21" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M21" s="13"/>
+      <x:c r="N21" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M21),L21&lt;&gt;"Shared bundle"),IF(L21="Full home run",K21,I21)+M21,"")</x:f>
+      </x:c>
+      <x:c r="O21" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P21" s="8" t="str">
+        <x:v>Buried duct below the entrance-hall floor and tower plinth, rising inside the solid tower pier to the cabinet. Duct size, depth, draw pits, water sealing and separation pending; no chase through the arch mouldings.</x:v>
+      </x:c>
+      <x:c r="Q21" s="9"/>
+      <x:c r="R21" s="9"/>
+      <x:c r="S21" s="13"/>
+      <x:c r="T21" s="9"/>
+      <x:c r="U21" s="9"/>
+      <x:c r="V21" s="9"/>
+      <x:c r="W21" s="9"/>
+      <x:c r="X21" s="9"/>
+      <x:c r="Y21" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="Z21" s="8" t="str">
+        <x:v>trunk:EB1:P4:power:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="90" customHeight="1">
+      <x:c r="A22" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B22" s="8" t="str">
+        <x:v>P3 · B · circuit trunk</x:v>
+      </x:c>
+      <x:c r="C22" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="D22" s="8" t="str">
+        <x:v>P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="E22" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="F22" s="8" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="G22" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H22" s="8" t="str">
+        <x:v>trunk</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A22,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>8.3</x:v>
+      </x:c>
+      <x:c r="J22" s="11"/>
+      <x:c r="K22" s="11" t="str">
+        <x:f>IF(L22="Full home run",I22+J22,"")</x:f>
+      </x:c>
+      <x:c r="L22" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M22" s="13"/>
+      <x:c r="N22" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M22),L22&lt;&gt;"Shared bundle"),IF(L22="Full home run",K22,I22)+M22,"")</x:f>
+      </x:c>
+      <x:c r="O22" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P22" s="8" t="str">
+        <x:v>Dedicated buried duct from DB-2 below the entrance-hall floor to the tower base; duct, depth, draw pits and water sealing pending.</x:v>
+      </x:c>
+      <x:c r="Q22" s="9"/>
+      <x:c r="R22" s="9"/>
+      <x:c r="S22" s="13"/>
+      <x:c r="T22" s="9"/>
+      <x:c r="U22" s="9"/>
+      <x:c r="V22" s="9"/>
+      <x:c r="W22" s="9"/>
+      <x:c r="X22" s="9"/>
+      <x:c r="Y22" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z22" s="8"/>
+    </x:row>
+    <x:row r="23" ht="90" customHeight="1">
+      <x:c r="A23" s="8" t="str">
+        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="str">
+        <x:v>P3 → Event power · tower B · inside the porch</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="D23" s="8" t="str">
+        <x:v>P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="E23" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="F23" s="8" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="G23" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H23" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A23,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>1.5699999999999994</x:v>
+      </x:c>
+      <x:c r="J23" s="11"/>
+      <x:c r="K23" s="11" t="str">
+        <x:f>IF(L23="Full home run",I23+J23,"")</x:f>
+      </x:c>
+      <x:c r="L23" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M23" s="13"/>
+      <x:c r="N23" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M23),L23&lt;&gt;"Shared bundle"),IF(L23="Full home run",K23,I23)+M23,"")</x:f>
+      </x:c>
+      <x:c r="O23" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P23" s="8" t="str">
+        <x:v>Buried duct below the entrance-hall floor and tower plinth, rising inside the solid tower pier to the cabinet. Duct size, depth, draw pits, water sealing and separation pending; no chase through the arch mouldings.</x:v>
+      </x:c>
+      <x:c r="Q23" s="9"/>
+      <x:c r="R23" s="9"/>
+      <x:c r="S23" s="13"/>
+      <x:c r="T23" s="9"/>
+      <x:c r="U23" s="9"/>
+      <x:c r="V23" s="9"/>
+      <x:c r="W23" s="9"/>
+      <x:c r="X23" s="9"/>
+      <x:c r="Y23" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z23" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="90" customHeight="1">
+      <x:c r="A24" s="8" t="str">
         <x:v>trunk:DB2:P4:power:1</x:v>
       </x:c>
+      <x:c r="B24" s="8" t="str">
+        <x:v>P4 · H · circuit trunk</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="D24" s="8" t="str">
+        <x:v>P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="E24" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="F24" s="8" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="G24" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H24" s="8" t="str">
+        <x:v>trunk</x:v>
+      </x:c>
+      <x:c r="I24" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A24,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>14.9</x:v>
+      </x:c>
+      <x:c r="J24" s="11"/>
+      <x:c r="K24" s="11" t="str">
+        <x:f>IF(L24="Full home run",I24+J24,"")</x:f>
+      </x:c>
+      <x:c r="L24" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M24" s="13"/>
+      <x:c r="N24" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M24),L24&lt;&gt;"Shared bundle"),IF(L24="Full home run",K24,I24)+M24,"")</x:f>
+      </x:c>
+      <x:c r="O24" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P24" s="8" t="str">
+        <x:v>Dedicated buried duct from DB-2 below the entrance-hall floor to the tower base; duct, depth, draw pits and water sealing pending.</x:v>
+      </x:c>
+      <x:c r="Q24" s="9"/>
+      <x:c r="R24" s="9"/>
+      <x:c r="S24" s="13"/>
+      <x:c r="T24" s="9"/>
+      <x:c r="U24" s="9"/>
+      <x:c r="V24" s="9"/>
+      <x:c r="W24" s="9"/>
+      <x:c r="X24" s="9"/>
+      <x:c r="Y24" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z24" s="8"/>
+    </x:row>
+    <x:row r="25" ht="90" customHeight="1">
+      <x:c r="A25" s="8" t="str">
+        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="str">
+        <x:v>P4 → Event power · tower H · inside the porch</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="D25" s="8" t="str">
+        <x:v>P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="E25" s="8" t="str">
+        <x:v>DB2</x:v>
+      </x:c>
+      <x:c r="F25" s="8" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="G25" s="8" t="str">
+        <x:v>power</x:v>
+      </x:c>
+      <x:c r="H25" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$129,A25,'Route Points'!$F$7:$F$129)</x:f>
+        <x:v>1.5699999999999994</x:v>
+      </x:c>
+      <x:c r="J25" s="11"/>
+      <x:c r="K25" s="11" t="str">
+        <x:f>IF(L25="Full home run",I25+J25,"")</x:f>
+      </x:c>
+      <x:c r="L25" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M25" s="13"/>
+      <x:c r="N25" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M25),L25&lt;&gt;"Shared bundle"),IF(L25="Full home run",K25,I25)+M25,"")</x:f>
+      </x:c>
+      <x:c r="O25" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P25" s="8" t="str">
+        <x:v>Buried duct below the entrance-hall floor and tower plinth, rising inside the solid tower pier to the cabinet. Duct size, depth, draw pits, water sealing and separation pending; no chase through the arch mouldings.</x:v>
+      </x:c>
+      <x:c r="Q25" s="9"/>
+      <x:c r="R25" s="9"/>
+      <x:c r="S25" s="13"/>
+      <x:c r="T25" s="9"/>
+      <x:c r="U25" s="9"/>
+      <x:c r="V25" s="9"/>
+      <x:c r="W25" s="9"/>
+      <x:c r="X25" s="9"/>
+      <x:c r="Y25" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z25" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="Y7:Y20">
+  <x:conditionalFormatting sqref="Y7:Y25">
     <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M20">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M25">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R20">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R25">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S20">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S25">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a70e8a7b90d4615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2b316d9ed8b4e07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3376,11 +3730,11 @@
         <x:v>7.65</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
         <x:f>SQRT((C27-C26)^2+(D27-D26)^2+(E27-E26)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>16.61</x:v>
       </x:c>
       <x:c r="G27" s="8" t="str">
         <x:v>Current</x:v>
@@ -3400,7 +3754,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
         <x:f>SQRT((C28-C27)^2+(D28-D27)^2+(E28-E27)^2)</x:f>
@@ -3418,17 +3772,17 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
         <x:f>SQRT((C29-C28)^2+(D29-D28)^2+(E29-E28)^2)</x:f>
-        <x:v>0.3799999999999999</x:v>
+        <x:v>2.1100000000000003</x:v>
       </x:c>
       <x:c r="G29" s="8" t="str">
         <x:v>Current</x:v>
@@ -3436,19 +3790,19 @@
     </x:row>
     <x:row r="30" ht="32" customHeight="1">
       <x:c r="A30" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:EB1</x:v>
       </x:c>
       <x:c r="B30" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
         <x:f>0</x:f>
@@ -3460,23 +3814,23 @@
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
       <x:c r="A31" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:EB1</x:v>
       </x:c>
       <x:c r="B31" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
         <x:f>SQRT((C31-C30)^2+(D31-D30)^2+(E31-E30)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>0.6000000000000001</x:v>
       </x:c>
       <x:c r="G31" s="8" t="str">
         <x:v>Current</x:v>
@@ -3484,23 +3838,23 @@
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
       <x:c r="A32" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:EB1</x:v>
       </x:c>
       <x:c r="B32" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
         <x:f>SQRT((C32-C31)^2+(D32-D31)^2+(E32-E31)^2)</x:f>
-        <x:v>0.6699999999999999</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="G32" s="8" t="str">
         <x:v>Current</x:v>
@@ -3508,23 +3862,23 @@
     </x:row>
     <x:row r="33" ht="32" customHeight="1">
       <x:c r="A33" s="8" t="str">
-        <x:v>feeder:AV1</x:v>
+        <x:v>feeder:EB1</x:v>
       </x:c>
       <x:c r="B33" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:f>SQRT((C33-C32)^2+(D33-D32)^2+(E33-E32)^2)</x:f>
-        <x:v>2.95</x:v>
+        <x:v>0.6000000000000001</x:v>
       </x:c>
       <x:c r="G33" s="8" t="str">
         <x:v>Current</x:v>
@@ -3535,20 +3889,20 @@
         <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B34" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:f>SQRT((C34-C33)^2+(D34-D33)^2+(E34-E33)^2)</x:f>
-        <x:v>1.47</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G34" s="8" t="str">
         <x:v>Current</x:v>
@@ -3559,20 +3913,20 @@
         <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B35" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
-        <x:v>49.275</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>0.95</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
         <x:f>SQRT((C35-C34)^2+(D35-D34)^2+(E35-E34)^2)</x:f>
-        <x:v>0.5399999999999991</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G35" s="8" t="str">
         <x:v>Current</x:v>
@@ -3580,23 +3934,23 @@
     </x:row>
     <x:row r="36" ht="32" customHeight="1">
       <x:c r="A36" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B36" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
         <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C36-C35)^2+(D36-D35)^2+(E36-E35)^2)</x:f>
+        <x:v>0.6699999999999999</x:v>
       </x:c>
       <x:c r="G36" s="8" t="str">
         <x:v>Current</x:v>
@@ -3604,23 +3958,23 @@
     </x:row>
     <x:row r="37" ht="32" customHeight="1">
       <x:c r="A37" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B37" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
         <x:f>SQRT((C37-C36)^2+(D37-D36)^2+(E37-E36)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="G37" s="8" t="str">
         <x:v>Current</x:v>
@@ -3628,23 +3982,23 @@
     </x:row>
     <x:row r="38" ht="32" customHeight="1">
       <x:c r="A38" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B38" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
         <x:f>SQRT((C38-C37)^2+(D38-D37)^2+(E38-E37)^2)</x:f>
-        <x:v>0.6699999999999999</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="G38" s="8" t="str">
         <x:v>Current</x:v>
@@ -3652,23 +4006,23 @@
     </x:row>
     <x:row r="39" ht="32" customHeight="1">
       <x:c r="A39" s="8" t="str">
-        <x:v>feeder:LC1</x:v>
+        <x:v>feeder:AV1</x:v>
       </x:c>
       <x:c r="B39" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>49.275</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:f>SQRT((C39-C38)^2+(D39-D38)^2+(E39-E38)^2)</x:f>
-        <x:v>1</x:v>
+        <x:v>0.5399999999999991</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>Current</x:v>
@@ -3679,20 +4033,20 @@
         <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B40" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:f>SQRT((C40-C39)^2+(D40-D39)^2+(E40-E39)^2)</x:f>
-        <x:v>0.5699999999999998</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G40" s="8" t="str">
         <x:v>Current</x:v>
@@ -3703,16 +4057,16 @@
         <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B41" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
         <x:f>SQRT((C41-C40)^2+(D41-D40)^2+(E41-E40)^2)</x:f>
@@ -3724,23 +4078,23 @@
     </x:row>
     <x:row r="42" ht="32" customHeight="1">
       <x:c r="A42" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B42" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
         <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C42-C41)^2+(D42-D41)^2+(E42-E41)^2)</x:f>
+        <x:v>0.6699999999999999</x:v>
       </x:c>
       <x:c r="G42" s="8" t="str">
         <x:v>Current</x:v>
@@ -3748,23 +4102,23 @@
     </x:row>
     <x:row r="43" ht="32" customHeight="1">
       <x:c r="A43" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B43" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
         <x:f>SQRT((C43-C42)^2+(D43-D42)^2+(E43-E42)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G43" s="8" t="str">
         <x:v>Current</x:v>
@@ -3772,23 +4126,23 @@
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
       <x:c r="A44" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B44" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
         <x:f>SQRT((C44-C43)^2+(D44-D43)^2+(E44-E43)^2)</x:f>
-        <x:v>0.6699999999999999</x:v>
+        <x:v>0.5699999999999998</x:v>
       </x:c>
       <x:c r="G44" s="8" t="str">
         <x:v>Current</x:v>
@@ -3796,23 +4150,23 @@
     </x:row>
     <x:row r="45" ht="32" customHeight="1">
       <x:c r="A45" s="8" t="str">
-        <x:v>feeder:FC1</x:v>
+        <x:v>feeder:LC1</x:v>
       </x:c>
       <x:c r="B45" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>2.42</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
         <x:f>SQRT((C45-C44)^2+(D45-D44)^2+(E45-E44)^2)</x:f>
-        <x:v>1.9500000000000002</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G45" s="8" t="str">
         <x:v>Current</x:v>
@@ -3823,20 +4177,20 @@
         <x:v>feeder:FC1</x:v>
       </x:c>
       <x:c r="B46" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:f>SQRT((C46-C45)^2+(D46-D45)^2+(E46-E45)^2)</x:f>
-        <x:v>0.47</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G46" s="8" t="str">
         <x:v>Current</x:v>
@@ -3847,16 +4201,16 @@
         <x:v>feeder:FC1</x:v>
       </x:c>
       <x:c r="B47" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>1.95</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
-        <x:v>0.4</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
         <x:f>SQRT((C47-C46)^2+(D47-D46)^2+(E47-E46)^2)</x:f>
@@ -3868,23 +4222,23 @@
     </x:row>
     <x:row r="48" ht="32" customHeight="1">
       <x:c r="A48" s="8" t="str">
-        <x:v>trunk:DB1:P1:power:-1</x:v>
+        <x:v>feeder:FC1</x:v>
       </x:c>
       <x:c r="B48" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
-        <x:v>48.895</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
         <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C48-C47)^2+(D48-D47)^2+(E48-E47)^2)</x:f>
+        <x:v>0.6699999999999999</x:v>
       </x:c>
       <x:c r="G48" s="8" t="str">
         <x:v>Current</x:v>
@@ -3892,23 +4246,23 @@
     </x:row>
     <x:row r="49" ht="32" customHeight="1">
       <x:c r="A49" s="8" t="str">
-        <x:v>trunk:DB1:P1:power:-1</x:v>
+        <x:v>feeder:FC1</x:v>
       </x:c>
       <x:c r="B49" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>-1.55</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
         <x:f>SQRT((C49-C48)^2+(D49-D48)^2+(E49-E48)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
+        <x:v>1.9500000000000002</x:v>
       </x:c>
       <x:c r="G49" s="8" t="str">
         <x:v>Current</x:v>
@@ -3916,23 +4270,23 @@
     </x:row>
     <x:row r="50" ht="32" customHeight="1">
       <x:c r="A50" s="8" t="str">
-        <x:v>trunk:DB1:P1:power:-1</x:v>
+        <x:v>feeder:FC1</x:v>
       </x:c>
       <x:c r="B50" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C50" s="11" t="n">
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F50" s="11" t="n">
         <x:f>SQRT((C50-C49)^2+(D50-D49)^2+(E50-E49)^2)</x:f>
-        <x:v>0.6900000000000002</x:v>
+        <x:v>0.47</x:v>
       </x:c>
       <x:c r="G50" s="8" t="str">
         <x:v>Current</x:v>
@@ -3940,23 +4294,23 @@
     </x:row>
     <x:row r="51" ht="32" customHeight="1">
       <x:c r="A51" s="8" t="str">
-        <x:v>trunk:DB1:P1:power:-1</x:v>
+        <x:v>feeder:FC1</x:v>
       </x:c>
       <x:c r="B51" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C51" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
         <x:f>SQRT((C51-C50)^2+(D51-D50)^2+(E51-E50)^2)</x:f>
-        <x:v>2.58</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G51" s="8" t="str">
         <x:v>Current</x:v>
@@ -3967,20 +4321,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B52" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C52" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D52" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E52" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F52" s="11" t="n">
-        <x:f>SQRT((C52-C51)^2+(D52-D51)^2+(E52-E51)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G52" s="8" t="str">
         <x:v>Current</x:v>
@@ -3991,20 +4345,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B53" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C53" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D53" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E53" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F53" s="11" t="n">
         <x:f>SQRT((C53-C52)^2+(D53-D52)^2+(E53-E52)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G53" s="8" t="str">
         <x:v>Current</x:v>
@@ -4015,20 +4369,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B54" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C54" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>6.1080000000000005</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E54" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F54" s="11" t="n">
         <x:f>SQRT((C54-C53)^2+(D54-D53)^2+(E54-E53)^2)</x:f>
-        <x:v>1.7780000000000005</x:v>
+        <x:v>0.6900000000000002</x:v>
       </x:c>
       <x:c r="G54" s="8" t="str">
         <x:v>Current</x:v>
@@ -4039,20 +4393,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B55" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C55" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>6.1080000000000005</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E55" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F55" s="11" t="n">
         <x:f>SQRT((C55-C54)^2+(D55-D54)^2+(E55-E54)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="G55" s="8" t="str">
         <x:v>Current</x:v>
@@ -4063,20 +4417,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B56" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C56" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>6.1080000000000005</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E56" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F56" s="11" t="n">
         <x:f>SQRT((C56-C55)^2+(D56-D55)^2+(E56-E55)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G56" s="8" t="str">
         <x:v>Current</x:v>
@@ -4087,20 +4441,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B57" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C57" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E57" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F57" s="11" t="n">
         <x:f>SQRT((C57-C56)^2+(D57-D56)^2+(E57-E56)^2)</x:f>
-        <x:v>0.9319999999999995</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G57" s="8" t="str">
         <x:v>Current</x:v>
@@ -4111,20 +4465,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B58" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C58" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.1080000000000005</x:v>
       </x:c>
       <x:c r="E58" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F58" s="11" t="n">
         <x:f>SQRT((C58-C57)^2+(D58-D57)^2+(E58-E57)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>1.7780000000000005</x:v>
       </x:c>
       <x:c r="G58" s="8" t="str">
         <x:v>Current</x:v>
@@ -4135,20 +4489,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B59" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C59" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>6.1080000000000005</x:v>
       </x:c>
       <x:c r="E59" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F59" s="11" t="n">
         <x:f>SQRT((C59-C58)^2+(D59-D58)^2+(E59-E58)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G59" s="8" t="str">
         <x:v>Current</x:v>
@@ -4159,20 +4513,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B60" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C60" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>6.1080000000000005</x:v>
       </x:c>
       <x:c r="E60" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F60" s="11" t="n">
         <x:f>SQRT((C60-C59)^2+(D60-D59)^2+(E60-E59)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G60" s="8" t="str">
         <x:v>Current</x:v>
@@ -4183,20 +4537,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B61" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C61" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E61" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F61" s="11" t="n">
         <x:f>SQRT((C61-C60)^2+(D61-D60)^2+(E61-E60)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>0.9319999999999995</x:v>
       </x:c>
       <x:c r="G61" s="8" t="str">
         <x:v>Current</x:v>
@@ -4207,10 +4561,10 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B62" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C62" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
         <x:v>7.04</x:v>
@@ -4220,7 +4574,7 @@
       </x:c>
       <x:c r="F62" s="11" t="n">
         <x:f>SQRT((C62-C61)^2+(D62-D61)^2+(E62-E61)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G62" s="8" t="str">
         <x:v>Current</x:v>
@@ -4231,20 +4585,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B63" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C63" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E63" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F63" s="11" t="n">
         <x:f>SQRT((C63-C62)^2+(D63-D62)^2+(E63-E62)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G63" s="8" t="str">
         <x:v>Current</x:v>
@@ -4255,20 +4609,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B64" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C64" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>6.1080000000000005</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E64" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F64" s="11" t="n">
         <x:f>SQRT((C64-C63)^2+(D64-D63)^2+(E64-E63)^2)</x:f>
-        <x:v>0.9319999999999995</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G64" s="8" t="str">
         <x:v>Current</x:v>
@@ -4279,20 +4633,20 @@
         <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B65" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C65" s="11" t="n">
-        <x:v>22.83</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>6.1080000000000005</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E65" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F65" s="11" t="n">
         <x:f>SQRT((C65-C64)^2+(D65-D64)^2+(E65-E64)^2)</x:f>
-        <x:v>14.145000000000003</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G65" s="8" t="str">
         <x:v>Current</x:v>
@@ -4300,23 +4654,23 @@
     </x:row>
     <x:row r="66" ht="32" customHeight="1">
       <x:c r="A66" s="8" t="str">
-        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+        <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B66" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C66" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>6.1080000000000005</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E66" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F66" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C66-C65)^2+(D66-D65)^2+(E66-E65)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G66" s="8" t="str">
         <x:v>Current</x:v>
@@ -4324,23 +4678,23 @@
     </x:row>
     <x:row r="67" ht="32" customHeight="1">
       <x:c r="A67" s="8" t="str">
-        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+        <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B67" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C67" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>0.85</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E67" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F67" s="11" t="n">
         <x:f>SQRT((C67-C66)^2+(D67-D66)^2+(E67-E66)^2)</x:f>
-        <x:v>5.258000000000001</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G67" s="8" t="str">
         <x:v>Current</x:v>
@@ -4348,23 +4702,23 @@
     </x:row>
     <x:row r="68" ht="32" customHeight="1">
       <x:c r="A68" s="8" t="str">
-        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+        <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B68" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C68" s="11" t="n">
-        <x:v>43.89</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>0.85</x:v>
+        <x:v>6.1080000000000005</x:v>
       </x:c>
       <x:c r="E68" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F68" s="11" t="n">
         <x:f>SQRT((C68-C67)^2+(D68-D67)^2+(E68-E67)^2)</x:f>
-        <x:v>0.2849999999999966</x:v>
+        <x:v>0.9319999999999995</x:v>
       </x:c>
       <x:c r="G68" s="8" t="str">
         <x:v>Current</x:v>
@@ -4372,23 +4726,23 @@
     </x:row>
     <x:row r="69" ht="32" customHeight="1">
       <x:c r="A69" s="8" t="str">
-        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
+        <x:v>trunk:DB1:P1:power:-1</x:v>
       </x:c>
       <x:c r="B69" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C69" s="11" t="n">
-        <x:v>43.89</x:v>
+        <x:v>22.83</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>0.85</x:v>
+        <x:v>6.1080000000000005</x:v>
       </x:c>
       <x:c r="E69" s="11" t="n">
-        <x:v>-7.25</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F69" s="11" t="n">
         <x:f>SQRT((C69-C68)^2+(D69-D68)^2+(E69-E68)^2)</x:f>
-        <x:v>0.11000000000000032</x:v>
+        <x:v>14.145000000000003</x:v>
       </x:c>
       <x:c r="G69" s="8" t="str">
         <x:v>Current</x:v>
@@ -4396,13 +4750,13 @@
     </x:row>
     <x:row r="70" ht="32" customHeight="1">
       <x:c r="A70" s="8" t="str">
-        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
       </x:c>
       <x:c r="B70" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C70" s="11" t="n">
-        <x:v>22.83</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
         <x:v>6.1080000000000005</x:v>
@@ -4420,23 +4774,23 @@
     </x:row>
     <x:row r="71" ht="32" customHeight="1">
       <x:c r="A71" s="8" t="str">
-        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
       </x:c>
       <x:c r="B71" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C71" s="11" t="n">
-        <x:v>22.83</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="E71" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F71" s="11" t="n">
         <x:f>SQRT((C71-C70)^2+(D71-D70)^2+(E71-E70)^2)</x:f>
-        <x:v>5.658</x:v>
+        <x:v>5.258000000000001</x:v>
       </x:c>
       <x:c r="G71" s="8" t="str">
         <x:v>Current</x:v>
@@ -4444,23 +4798,23 @@
     </x:row>
     <x:row r="72" ht="32" customHeight="1">
       <x:c r="A72" s="8" t="str">
-        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
       </x:c>
       <x:c r="B72" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C72" s="11" t="n">
-        <x:v>22.83</x:v>
+        <x:v>43.89</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="E72" s="11" t="n">
-        <x:v>-7.25</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F72" s="11" t="n">
         <x:f>SQRT((C72-C71)^2+(D72-D71)^2+(E72-E71)^2)</x:f>
-        <x:v>0.11000000000000032</x:v>
+        <x:v>0.2849999999999966</x:v>
       </x:c>
       <x:c r="G72" s="8" t="str">
         <x:v>Current</x:v>
@@ -4468,71 +4822,71 @@
     </x:row>
     <x:row r="73" ht="32" customHeight="1">
       <x:c r="A73" s="8" t="str">
-        <x:v>trunk:DB2:P3:power:-1</x:v>
+        <x:v>drop:DB1:P1:power:-1:P-SANCT-B</x:v>
       </x:c>
       <x:c r="B73" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C73" s="11" t="n">
+        <x:v>43.89</x:v>
+      </x:c>
+      <x:c r="D73" s="11" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E73" s="11" t="n">
+        <x:v>-7.25</x:v>
+      </x:c>
+      <x:c r="F73" s="11" t="n">
+        <x:f>SQRT((C73-C72)^2+(D73-D72)^2+(E73-E72)^2)</x:f>
+        <x:v>0.11000000000000032</x:v>
+      </x:c>
+      <x:c r="G73" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="32" customHeight="1">
+      <x:c r="A74" s="8" t="str">
+        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
+      </x:c>
+      <x:c r="B74" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C73" s="11" t="n">
-        <x:v>2.73</x:v>
-      </x:c>
-      <x:c r="D73" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="E73" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F73" s="11" t="n">
+      <x:c r="C74" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D74" s="11" t="n">
+        <x:v>6.1080000000000005</x:v>
+      </x:c>
+      <x:c r="E74" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F74" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G73" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="32" customHeight="1">
-      <x:c r="A74" s="8" t="str">
-        <x:v>trunk:DB2:P3:power:-1</x:v>
-      </x:c>
-      <x:c r="B74" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C74" s="11" t="n">
-        <x:v>2.73</x:v>
-      </x:c>
-      <x:c r="D74" s="11" t="n">
-        <x:v>-0.12</x:v>
-      </x:c>
-      <x:c r="E74" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F74" s="11" t="n">
-        <x:f>SQRT((C74-C73)^2+(D74-D73)^2+(E74-E73)^2)</x:f>
-        <x:v>1.62</x:v>
-      </x:c>
       <x:c r="G74" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="32" customHeight="1">
       <x:c r="A75" s="8" t="str">
-        <x:v>trunk:DB2:P3:power:-1</x:v>
+        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
       </x:c>
       <x:c r="B75" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C75" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>22.83</x:v>
       </x:c>
       <x:c r="D75" s="11" t="n">
-        <x:v>-0.12</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="E75" s="11" t="n">
-        <x:v>-7.7</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F75" s="11" t="n">
         <x:f>SQRT((C75-C74)^2+(D75-D74)^2+(E75-E74)^2)</x:f>
-        <x:v>4.4</x:v>
+        <x:v>5.658</x:v>
       </x:c>
       <x:c r="G75" s="8" t="str">
         <x:v>Current</x:v>
@@ -4540,23 +4894,23 @@
     </x:row>
     <x:row r="76" ht="32" customHeight="1">
       <x:c r="A76" s="8" t="str">
-        <x:v>trunk:DB2:P3:power:-1</x:v>
+        <x:v>drop:DB1:P1:power:-1:P-NAVE-B</x:v>
       </x:c>
       <x:c r="B76" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C76" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D76" s="11" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="D76" s="11" t="n">
-        <x:v>-0.12</x:v>
-      </x:c>
       <x:c r="E76" s="11" t="n">
-        <x:v>-7.7</x:v>
+        <x:v>-7.25</x:v>
       </x:c>
       <x:c r="F76" s="11" t="n">
         <x:f>SQRT((C76-C75)^2+(D76-D75)^2+(E76-E75)^2)</x:f>
-        <x:v>2.28</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G76" s="8" t="str">
         <x:v>Current</x:v>
@@ -4564,19 +4918,19 @@
     </x:row>
     <x:row r="77" ht="32" customHeight="1">
       <x:c r="A77" s="8" t="str">
-        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+        <x:v>trunk:EB1:P3:power:-1</x:v>
       </x:c>
       <x:c r="B77" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C77" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
-        <x:v>-0.12</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E77" s="11" t="n">
-        <x:v>-7.7</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="F77" s="11" t="n">
         <x:f>0</x:f>
@@ -4588,23 +4942,23 @@
     </x:row>
     <x:row r="78" ht="32" customHeight="1">
       <x:c r="A78" s="8" t="str">
-        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+        <x:v>trunk:EB1:P3:power:-1</x:v>
       </x:c>
       <x:c r="B78" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C78" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>1.3</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="E78" s="11" t="n">
-        <x:v>-7.7</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="F78" s="11" t="n">
         <x:f>SQRT((C78-C77)^2+(D78-D77)^2+(E78-E77)^2)</x:f>
-        <x:v>1.42</x:v>
+        <x:v>1.62</x:v>
       </x:c>
       <x:c r="G78" s="8" t="str">
         <x:v>Current</x:v>
@@ -4612,23 +4966,23 @@
     </x:row>
     <x:row r="79" ht="32" customHeight="1">
       <x:c r="A79" s="8" t="str">
-        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+        <x:v>trunk:EB1:P3:power:-1</x:v>
       </x:c>
       <x:c r="B79" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C79" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
-        <x:v>1.3</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="E79" s="11" t="n">
-        <x:v>-7.85</x:v>
+        <x:v>-7.7</x:v>
       </x:c>
       <x:c r="F79" s="11" t="n">
         <x:f>SQRT((C79-C78)^2+(D79-D78)^2+(E79-E78)^2)</x:f>
-        <x:v>0.14999999999999947</x:v>
+        <x:v>18.45</x:v>
       </x:c>
       <x:c r="G79" s="8" t="str">
         <x:v>Current</x:v>
@@ -4636,71 +4990,71 @@
     </x:row>
     <x:row r="80" ht="32" customHeight="1">
       <x:c r="A80" s="8" t="str">
-        <x:v>trunk:DB1:P2:power:1</x:v>
+        <x:v>trunk:EB1:P3:power:-1</x:v>
       </x:c>
       <x:c r="B80" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C80" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D80" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E80" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F80" s="11" t="n">
+        <x:f>SQRT((C80-C79)^2+(D80-D79)^2+(E80-E79)^2)</x:f>
+        <x:v>0.21000000000000002</x:v>
+      </x:c>
+      <x:c r="G80" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="32" customHeight="1">
+      <x:c r="A81" s="8" t="str">
+        <x:v>drop:EB1:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="B81" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C80" s="11" t="n">
-        <x:v>48.895</x:v>
-      </x:c>
-      <x:c r="D80" s="11" t="n">
-        <x:v>1.75</x:v>
-      </x:c>
-      <x:c r="E80" s="11" t="n">
-        <x:v>-1.55</x:v>
-      </x:c>
-      <x:c r="F80" s="11" t="n">
+      <x:c r="C81" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D81" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E81" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F81" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G80" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="32" customHeight="1">
-      <x:c r="A81" s="8" t="str">
-        <x:v>trunk:DB1:P2:power:1</x:v>
-      </x:c>
-      <x:c r="B81" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C81" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D81" s="11" t="n">
-        <x:v>1.75</x:v>
-      </x:c>
-      <x:c r="E81" s="11" t="n">
-        <x:v>-1.55</x:v>
-      </x:c>
-      <x:c r="F81" s="11" t="n">
-        <x:f>SQRT((C81-C80)^2+(D81-D80)^2+(E81-E80)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
-      </x:c>
       <x:c r="G81" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="32" customHeight="1">
       <x:c r="A82" s="8" t="str">
-        <x:v>trunk:DB1:P2:power:1</x:v>
+        <x:v>drop:EB1:P3:power:-1:P-TOWER-B</x:v>
       </x:c>
       <x:c r="B82" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C82" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="E82" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.7</x:v>
       </x:c>
       <x:c r="F82" s="11" t="n">
         <x:f>SQRT((C82-C81)^2+(D82-D81)^2+(E82-E81)^2)</x:f>
-        <x:v>0.6900000000000002</x:v>
+        <x:v>1.42</x:v>
       </x:c>
       <x:c r="G82" s="8" t="str">
         <x:v>Current</x:v>
@@ -4708,23 +5062,23 @@
     </x:row>
     <x:row r="83" ht="32" customHeight="1">
       <x:c r="A83" s="8" t="str">
-        <x:v>trunk:DB1:P2:power:1</x:v>
+        <x:v>drop:EB1:P3:power:-1:P-TOWER-B</x:v>
       </x:c>
       <x:c r="B83" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C83" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="E83" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.85</x:v>
       </x:c>
       <x:c r="F83" s="11" t="n">
         <x:f>SQRT((C83-C82)^2+(D83-D82)^2+(E83-E82)^2)</x:f>
-        <x:v>2.58</x:v>
+        <x:v>0.14999999999999947</x:v>
       </x:c>
       <x:c r="G83" s="8" t="str">
         <x:v>Current</x:v>
@@ -4735,20 +5089,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B84" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C84" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E84" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F84" s="11" t="n">
-        <x:f>SQRT((C84-C83)^2+(D84-D83)^2+(E84-E83)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G84" s="8" t="str">
         <x:v>Current</x:v>
@@ -4759,20 +5113,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B85" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C85" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E85" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F85" s="11" t="n">
         <x:f>SQRT((C85-C84)^2+(D85-D84)^2+(E85-E84)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G85" s="8" t="str">
         <x:v>Current</x:v>
@@ -4783,20 +5137,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B86" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C86" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>6.1160000000000005</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E86" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F86" s="11" t="n">
         <x:f>SQRT((C86-C85)^2+(D86-D85)^2+(E86-E85)^2)</x:f>
-        <x:v>1.7860000000000005</x:v>
+        <x:v>0.6900000000000002</x:v>
       </x:c>
       <x:c r="G86" s="8" t="str">
         <x:v>Current</x:v>
@@ -4807,20 +5161,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B87" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C87" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>6.1160000000000005</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E87" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F87" s="11" t="n">
         <x:f>SQRT((C87-C86)^2+(D87-D86)^2+(E87-E86)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="G87" s="8" t="str">
         <x:v>Current</x:v>
@@ -4831,20 +5185,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B88" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C88" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>6.1160000000000005</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E88" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F88" s="11" t="n">
         <x:f>SQRT((C88-C87)^2+(D88-D87)^2+(E88-E87)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G88" s="8" t="str">
         <x:v>Current</x:v>
@@ -4855,20 +5209,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B89" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C89" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E89" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F89" s="11" t="n">
         <x:f>SQRT((C89-C88)^2+(D89-D88)^2+(E89-E88)^2)</x:f>
-        <x:v>0.9239999999999995</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G89" s="8" t="str">
         <x:v>Current</x:v>
@@ -4879,20 +5233,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B90" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C90" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.1160000000000005</x:v>
       </x:c>
       <x:c r="E90" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F90" s="11" t="n">
         <x:f>SQRT((C90-C89)^2+(D90-D89)^2+(E90-E89)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>1.7860000000000005</x:v>
       </x:c>
       <x:c r="G90" s="8" t="str">
         <x:v>Current</x:v>
@@ -4903,20 +5257,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B91" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C91" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>6.1160000000000005</x:v>
       </x:c>
       <x:c r="E91" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F91" s="11" t="n">
         <x:f>SQRT((C91-C90)^2+(D91-D90)^2+(E91-E90)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G91" s="8" t="str">
         <x:v>Current</x:v>
@@ -4927,20 +5281,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B92" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C92" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>6.1160000000000005</x:v>
       </x:c>
       <x:c r="E92" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F92" s="11" t="n">
         <x:f>SQRT((C92-C91)^2+(D92-D91)^2+(E92-E91)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G92" s="8" t="str">
         <x:v>Current</x:v>
@@ -4951,20 +5305,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B93" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C93" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E93" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F93" s="11" t="n">
         <x:f>SQRT((C93-C92)^2+(D93-D92)^2+(E93-E92)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>0.9239999999999995</x:v>
       </x:c>
       <x:c r="G93" s="8" t="str">
         <x:v>Current</x:v>
@@ -4975,10 +5329,10 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B94" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C94" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D94" s="11" t="n">
         <x:v>7.04</x:v>
@@ -4988,7 +5342,7 @@
       </x:c>
       <x:c r="F94" s="11" t="n">
         <x:f>SQRT((C94-C93)^2+(D94-D93)^2+(E94-E93)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G94" s="8" t="str">
         <x:v>Current</x:v>
@@ -4999,20 +5353,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B95" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C95" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D95" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E95" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F95" s="11" t="n">
         <x:f>SQRT((C95-C94)^2+(D95-D94)^2+(E95-E94)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G95" s="8" t="str">
         <x:v>Current</x:v>
@@ -5023,20 +5377,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B96" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C96" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D96" s="11" t="n">
-        <x:v>6.1160000000000005</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E96" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F96" s="11" t="n">
         <x:f>SQRT((C96-C95)^2+(D96-D95)^2+(E96-E95)^2)</x:f>
-        <x:v>0.9239999999999995</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G96" s="8" t="str">
         <x:v>Current</x:v>
@@ -5047,20 +5401,20 @@
         <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B97" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C97" s="11" t="n">
-        <x:v>22.83</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D97" s="11" t="n">
-        <x:v>6.1160000000000005</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E97" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F97" s="11" t="n">
         <x:f>SQRT((C97-C96)^2+(D97-D96)^2+(E97-E96)^2)</x:f>
-        <x:v>14.145000000000003</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G97" s="8" t="str">
         <x:v>Current</x:v>
@@ -5068,23 +5422,23 @@
     </x:row>
     <x:row r="98" ht="32" customHeight="1">
       <x:c r="A98" s="8" t="str">
-        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+        <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B98" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C98" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
-        <x:v>6.1160000000000005</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E98" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F98" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C98-C97)^2+(D98-D97)^2+(E98-E97)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G98" s="8" t="str">
         <x:v>Current</x:v>
@@ -5092,23 +5446,23 @@
     </x:row>
     <x:row r="99" ht="32" customHeight="1">
       <x:c r="A99" s="8" t="str">
-        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+        <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B99" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C99" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
-        <x:v>0.85</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E99" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F99" s="11" t="n">
         <x:f>SQRT((C99-C98)^2+(D99-D98)^2+(E99-E98)^2)</x:f>
-        <x:v>5.266000000000001</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G99" s="8" t="str">
         <x:v>Current</x:v>
@@ -5116,23 +5470,23 @@
     </x:row>
     <x:row r="100" ht="32" customHeight="1">
       <x:c r="A100" s="8" t="str">
-        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+        <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B100" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C100" s="11" t="n">
-        <x:v>43.89</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>0.85</x:v>
+        <x:v>6.1160000000000005</x:v>
       </x:c>
       <x:c r="E100" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F100" s="11" t="n">
         <x:f>SQRT((C100-C99)^2+(D100-D99)^2+(E100-E99)^2)</x:f>
-        <x:v>0.2849999999999966</x:v>
+        <x:v>0.9239999999999995</x:v>
       </x:c>
       <x:c r="G100" s="8" t="str">
         <x:v>Current</x:v>
@@ -5140,23 +5494,23 @@
     </x:row>
     <x:row r="101" ht="32" customHeight="1">
       <x:c r="A101" s="8" t="str">
-        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
+        <x:v>trunk:DB1:P2:power:1</x:v>
       </x:c>
       <x:c r="B101" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C101" s="11" t="n">
-        <x:v>43.89</x:v>
+        <x:v>22.83</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>0.85</x:v>
+        <x:v>6.1160000000000005</x:v>
       </x:c>
       <x:c r="E101" s="11" t="n">
-        <x:v>7.25</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F101" s="11" t="n">
         <x:f>SQRT((C101-C100)^2+(D101-D100)^2+(E101-E100)^2)</x:f>
-        <x:v>0.11000000000000032</x:v>
+        <x:v>14.145000000000003</x:v>
       </x:c>
       <x:c r="G101" s="8" t="str">
         <x:v>Current</x:v>
@@ -5164,13 +5518,13 @@
     </x:row>
     <x:row r="102" ht="32" customHeight="1">
       <x:c r="A102" s="8" t="str">
-        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
       </x:c>
       <x:c r="B102" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C102" s="11" t="n">
-        <x:v>22.83</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
         <x:v>6.1160000000000005</x:v>
@@ -5188,23 +5542,23 @@
     </x:row>
     <x:row r="103" ht="32" customHeight="1">
       <x:c r="A103" s="8" t="str">
-        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
       </x:c>
       <x:c r="B103" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C103" s="11" t="n">
-        <x:v>22.83</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="E103" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F103" s="11" t="n">
         <x:f>SQRT((C103-C102)^2+(D103-D102)^2+(E103-E102)^2)</x:f>
-        <x:v>5.666</x:v>
+        <x:v>5.266000000000001</x:v>
       </x:c>
       <x:c r="G103" s="8" t="str">
         <x:v>Current</x:v>
@@ -5212,23 +5566,23 @@
     </x:row>
     <x:row r="104" ht="32" customHeight="1">
       <x:c r="A104" s="8" t="str">
-        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
       </x:c>
       <x:c r="B104" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C104" s="11" t="n">
-        <x:v>22.83</x:v>
+        <x:v>43.89</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="E104" s="11" t="n">
-        <x:v>7.25</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F104" s="11" t="n">
         <x:f>SQRT((C104-C103)^2+(D104-D103)^2+(E104-E103)^2)</x:f>
-        <x:v>0.11000000000000032</x:v>
+        <x:v>0.2849999999999966</x:v>
       </x:c>
       <x:c r="G104" s="8" t="str">
         <x:v>Current</x:v>
@@ -5236,71 +5590,71 @@
     </x:row>
     <x:row r="105" ht="32" customHeight="1">
       <x:c r="A105" s="8" t="str">
-        <x:v>trunk:DB2:P4:power:1</x:v>
+        <x:v>drop:DB1:P2:power:1:P-SANCT-H</x:v>
       </x:c>
       <x:c r="B105" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C105" s="11" t="n">
+        <x:v>43.89</x:v>
+      </x:c>
+      <x:c r="D105" s="11" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="E105" s="11" t="n">
+        <x:v>7.25</x:v>
+      </x:c>
+      <x:c r="F105" s="11" t="n">
+        <x:f>SQRT((C105-C104)^2+(D105-D104)^2+(E105-E104)^2)</x:f>
+        <x:v>0.11000000000000032</x:v>
+      </x:c>
+      <x:c r="G105" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="32" customHeight="1">
+      <x:c r="A106" s="8" t="str">
+        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
+      </x:c>
+      <x:c r="B106" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C105" s="11" t="n">
-        <x:v>2.73</x:v>
-      </x:c>
-      <x:c r="D105" s="11" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="E105" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F105" s="11" t="n">
+      <x:c r="C106" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D106" s="11" t="n">
+        <x:v>6.1160000000000005</x:v>
+      </x:c>
+      <x:c r="E106" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F106" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G105" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" ht="32" customHeight="1">
-      <x:c r="A106" s="8" t="str">
-        <x:v>trunk:DB2:P4:power:1</x:v>
-      </x:c>
-      <x:c r="B106" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C106" s="11" t="n">
-        <x:v>2.73</x:v>
-      </x:c>
-      <x:c r="D106" s="11" t="n">
-        <x:v>-0.12</x:v>
-      </x:c>
-      <x:c r="E106" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F106" s="11" t="n">
-        <x:f>SQRT((C106-C105)^2+(D106-D105)^2+(E106-E105)^2)</x:f>
-        <x:v>1.62</x:v>
-      </x:c>
       <x:c r="G106" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="32" customHeight="1">
       <x:c r="A107" s="8" t="str">
-        <x:v>trunk:DB2:P4:power:1</x:v>
+        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
       </x:c>
       <x:c r="B107" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C107" s="11" t="n">
-        <x:v>2.73</x:v>
+        <x:v>22.83</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>-0.12</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="E107" s="11" t="n">
-        <x:v>7.7</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F107" s="11" t="n">
         <x:f>SQRT((C107-C106)^2+(D107-D106)^2+(E107-E106)^2)</x:f>
-        <x:v>11</x:v>
+        <x:v>5.666</x:v>
       </x:c>
       <x:c r="G107" s="8" t="str">
         <x:v>Current</x:v>
@@ -5308,23 +5662,23 @@
     </x:row>
     <x:row r="108" ht="32" customHeight="1">
       <x:c r="A108" s="8" t="str">
-        <x:v>trunk:DB2:P4:power:1</x:v>
+        <x:v>drop:DB1:P2:power:1:P-NAVE-H</x:v>
       </x:c>
       <x:c r="B108" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C108" s="11" t="n">
+        <x:v>22.83</x:v>
+      </x:c>
+      <x:c r="D108" s="11" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="D108" s="11" t="n">
-        <x:v>-0.12</x:v>
-      </x:c>
       <x:c r="E108" s="11" t="n">
-        <x:v>7.7</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="F108" s="11" t="n">
         <x:f>SQRT((C108-C107)^2+(D108-D107)^2+(E108-E107)^2)</x:f>
-        <x:v>2.28</x:v>
+        <x:v>0.11000000000000032</x:v>
       </x:c>
       <x:c r="G108" s="8" t="str">
         <x:v>Current</x:v>
@@ -5332,19 +5686,19 @@
     </x:row>
     <x:row r="109" ht="32" customHeight="1">
       <x:c r="A109" s="8" t="str">
-        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+        <x:v>trunk:EB1:P4:power:1</x:v>
       </x:c>
       <x:c r="B109" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C109" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>-0.12</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E109" s="11" t="n">
-        <x:v>7.7</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="F109" s="11" t="n">
         <x:f>0</x:f>
@@ -5356,23 +5710,23 @@
     </x:row>
     <x:row r="110" ht="32" customHeight="1">
       <x:c r="A110" s="8" t="str">
-        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+        <x:v>trunk:EB1:P4:power:1</x:v>
       </x:c>
       <x:c r="B110" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C110" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>1.3</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="E110" s="11" t="n">
-        <x:v>7.7</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="F110" s="11" t="n">
         <x:f>SQRT((C110-C109)^2+(D110-D109)^2+(E110-E109)^2)</x:f>
-        <x:v>1.42</x:v>
+        <x:v>1.62</x:v>
       </x:c>
       <x:c r="G110" s="8" t="str">
         <x:v>Current</x:v>
@@ -5380,35 +5734,467 @@
     </x:row>
     <x:row r="111" ht="32" customHeight="1">
       <x:c r="A111" s="8" t="str">
-        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+        <x:v>trunk:EB1:P4:power:1</x:v>
       </x:c>
       <x:c r="B111" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C111" s="11" t="n">
-        <x:v>0.45</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>1.3</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="E111" s="11" t="n">
-        <x:v>7.85</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="F111" s="11" t="n">
         <x:f>SQRT((C111-C110)^2+(D111-D110)^2+(E111-E110)^2)</x:f>
+        <x:v>3.05</x:v>
+      </x:c>
+      <x:c r="G111" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="32" customHeight="1">
+      <x:c r="A112" s="8" t="str">
+        <x:v>trunk:EB1:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B112" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C112" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D112" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E112" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F112" s="11" t="n">
+        <x:f>SQRT((C112-C111)^2+(D112-D111)^2+(E112-E111)^2)</x:f>
+        <x:v>0.21000000000000002</x:v>
+      </x:c>
+      <x:c r="G112" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="32" customHeight="1">
+      <x:c r="A113" s="8" t="str">
+        <x:v>drop:EB1:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B113" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C113" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D113" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E113" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F113" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G113" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="32" customHeight="1">
+      <x:c r="A114" s="8" t="str">
+        <x:v>drop:EB1:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B114" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C114" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D114" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E114" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F114" s="11" t="n">
+        <x:f>SQRT((C114-C113)^2+(D114-D113)^2+(E114-E113)^2)</x:f>
+        <x:v>1.42</x:v>
+      </x:c>
+      <x:c r="G114" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="32" customHeight="1">
+      <x:c r="A115" s="8" t="str">
+        <x:v>drop:EB1:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B115" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C115" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D115" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E115" s="11" t="n">
+        <x:v>7.85</x:v>
+      </x:c>
+      <x:c r="F115" s="11" t="n">
+        <x:f>SQRT((C115-C114)^2+(D115-D114)^2+(E115-E114)^2)</x:f>
         <x:v>0.14999999999999947</x:v>
       </x:c>
-      <x:c r="G111" s="8" t="str">
-        <x:v>Current</x:v>
+      <x:c r="G115" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="32" customHeight="1">
+      <x:c r="A116" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B116" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C116" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D116" s="11" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E116" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F116" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G116" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="32" customHeight="1">
+      <x:c r="A117" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B117" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C117" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D117" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E117" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F117" s="11" t="n">
+        <x:f>SQRT((C117-C116)^2+(D117-D116)^2+(E117-E116)^2)</x:f>
+        <x:v>1.62</x:v>
+      </x:c>
+      <x:c r="G117" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="32" customHeight="1">
+      <x:c r="A118" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B118" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C118" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D118" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E118" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F118" s="11" t="n">
+        <x:f>SQRT((C118-C117)^2+(D118-D117)^2+(E118-E117)^2)</x:f>
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="G118" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="32" customHeight="1">
+      <x:c r="A119" s="8" t="str">
+        <x:v>trunk:DB2:P3:power:-1</x:v>
+      </x:c>
+      <x:c r="B119" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C119" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D119" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E119" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F119" s="11" t="n">
+        <x:f>SQRT((C119-C118)^2+(D119-D118)^2+(E119-E118)^2)</x:f>
+        <x:v>2.28</x:v>
+      </x:c>
+      <x:c r="G119" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="32" customHeight="1">
+      <x:c r="A120" s="8" t="str">
+        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="B120" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C120" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D120" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E120" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F120" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G120" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="32" customHeight="1">
+      <x:c r="A121" s="8" t="str">
+        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="B121" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C121" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D121" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E121" s="11" t="n">
+        <x:v>-7.7</x:v>
+      </x:c>
+      <x:c r="F121" s="11" t="n">
+        <x:f>SQRT((C121-C120)^2+(D121-D120)^2+(E121-E120)^2)</x:f>
+        <x:v>1.42</x:v>
+      </x:c>
+      <x:c r="G121" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="32" customHeight="1">
+      <x:c r="A122" s="8" t="str">
+        <x:v>drop:DB2:P3:power:-1:P-TOWER-B</x:v>
+      </x:c>
+      <x:c r="B122" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C122" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D122" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E122" s="11" t="n">
+        <x:v>-7.85</x:v>
+      </x:c>
+      <x:c r="F122" s="11" t="n">
+        <x:f>SQRT((C122-C121)^2+(D122-D121)^2+(E122-E121)^2)</x:f>
+        <x:v>0.14999999999999947</x:v>
+      </x:c>
+      <x:c r="G122" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="32" customHeight="1">
+      <x:c r="A123" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B123" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C123" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D123" s="11" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E123" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F123" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G123" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="32" customHeight="1">
+      <x:c r="A124" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B124" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C124" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D124" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E124" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F124" s="11" t="n">
+        <x:f>SQRT((C124-C123)^2+(D124-D123)^2+(E124-E123)^2)</x:f>
+        <x:v>1.62</x:v>
+      </x:c>
+      <x:c r="G124" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="32" customHeight="1">
+      <x:c r="A125" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B125" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C125" s="11" t="n">
+        <x:v>2.73</x:v>
+      </x:c>
+      <x:c r="D125" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E125" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F125" s="11" t="n">
+        <x:f>SQRT((C125-C124)^2+(D125-D124)^2+(E125-E124)^2)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G125" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="32" customHeight="1">
+      <x:c r="A126" s="8" t="str">
+        <x:v>trunk:DB2:P4:power:1</x:v>
+      </x:c>
+      <x:c r="B126" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C126" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D126" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E126" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F126" s="11" t="n">
+        <x:f>SQRT((C126-C125)^2+(D126-D125)^2+(E126-E125)^2)</x:f>
+        <x:v>2.28</x:v>
+      </x:c>
+      <x:c r="G126" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="32" customHeight="1">
+      <x:c r="A127" s="8" t="str">
+        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B127" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C127" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D127" s="11" t="n">
+        <x:v>-0.12</x:v>
+      </x:c>
+      <x:c r="E127" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F127" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G127" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="32" customHeight="1">
+      <x:c r="A128" s="8" t="str">
+        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B128" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C128" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D128" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E128" s="11" t="n">
+        <x:v>7.7</x:v>
+      </x:c>
+      <x:c r="F128" s="11" t="n">
+        <x:f>SQRT((C128-C127)^2+(D128-D127)^2+(E128-E127)^2)</x:f>
+        <x:v>1.42</x:v>
+      </x:c>
+      <x:c r="G128" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="32" customHeight="1">
+      <x:c r="A129" s="8" t="str">
+        <x:v>drop:DB2:P4:power:1:P-TOWER-H</x:v>
+      </x:c>
+      <x:c r="B129" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C129" s="11" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D129" s="11" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E129" s="11" t="n">
+        <x:v>7.85</x:v>
+      </x:c>
+      <x:c r="F129" s="11" t="n">
+        <x:f>SQRT((C129-C128)^2+(D129-D128)^2+(E129-E128)^2)</x:f>
+        <x:v>0.14999999999999947</x:v>
+      </x:c>
+      <x:c r="G129" s="8" t="str">
+        <x:v>Retired</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G111">
+  <x:conditionalFormatting sqref="G7:G129">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4b1e74726e34007"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd743881ffd7d4645"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R54dfc2f01da54f2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcc99cbf9c64e48b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R17abe80a8a9c4a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb8bc0581c4fa48b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3a50b29084af474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R2d335f05e5584b91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re579c9c22ae14b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rda60e2bef062485c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
+        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
+        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1731,7 +1731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R328662b1a11846b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba217b1f31934d98"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3142,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2b316d9ed8b4e07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc76320319a8d4fc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6194,7 +6194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd743881ffd7d4645"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf300ead89ba04a7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3a50b29084af474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R2d335f05e5584b91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re579c9c22ae14b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rda60e2bef062485c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R44fe7823c24447fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R37421f55e5154d87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3ffddcfac87944e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R74c6ce5c21d24b97"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
+        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -1731,7 +1731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba217b1f31934d98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bc851fcafe247be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3142,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc76320319a8d4fc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb9bc3ad4edc4ece"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6194,7 +6194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf300ead89ba04a7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra097ecfe485b4501"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R44fe7823c24447fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R37421f55e5154d87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3ffddcfac87944e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R74c6ce5c21d24b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3f12ee9dc63a4926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re54e61768c374c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R4dfbea40b5ff4f36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R47bf582e3a2e4b79"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T22:22:25.930Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
+        <x:v>325f8ef8696abef155a85a11a511a71ee5bbd155d28b2e0bfd11928b39ade4e3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
+        <x:v>75fa53533f9758516132ea54608152663cd0f407a24b0e6a3e030bc743a6ab27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1731,7 +1731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bc851fcafe247be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d42489abee74e6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3142,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb9bc3ad4edc4ece"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e02a37fb43648d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6194,7 +6194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra097ecfe485b4501"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd2ca0f7d8c34aca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3f12ee9dc63a4926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re54e61768c374c0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R4dfbea40b5ff4f36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R47bf582e3a2e4b79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R664fce651d0c4dcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R37b77c786dce41a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R274761c9a90245f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R402502a37ffe44d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-24T22:22:25.930Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-25T11:43:35.202Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>325f8ef8696abef155a85a11a511a71ee5bbd155d28b2e0bfd11928b39ade4e3</x:v>
+        <x:v>8794d15eced755667fbb94a78904d0b24ab39e7c75d28fc3bbe150bece4e8ceb</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>75fa53533f9758516132ea54608152663cd0f407a24b0e6a3e030bc743a6ab27</x:v>
+        <x:v>fa54e193a88aab1a463c7e9a9d929aac8295554193f697131ae924624c8c3635</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1731,7 +1731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d42489abee74e6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rced124c5f05145a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3142,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e02a37fb43648d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1408a4f8af454846"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6194,7 +6194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd2ca0f7d8c34aca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c439b10d81d45ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R664fce651d0c4dcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R37b77c786dce41a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R274761c9a90245f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R402502a37ffe44d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R07430fac345b46e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb3bbff601f4f4540"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0b0a1815b1dd4894"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R5115b96af18a4475"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-25T11:43:35.202Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8794d15eced755667fbb94a78904d0b24ab39e7c75d28fc3bbe150bece4e8ceb</x:v>
+        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fa54e193a88aab1a463c7e9a9d929aac8295554193f697131ae924624c8c3635</x:v>
+        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1731,7 +1731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rced124c5f05145a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c5b821f5693461f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3142,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1408a4f8af454846"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b7291ef17e418a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6194,7 +6194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c439b10d81d45ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9db2bdfe27034f8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R07430fac345b46e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb3bbff601f4f4540"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R0b0a1815b1dd4894"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R5115b96af18a4475"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re5c526ae30414228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9331e8f1633e4806"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R610a0aed92194aa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R35557bf75fbb46ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
+        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
+        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1731,7 +1731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c5b821f5693461f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1a4a18e33e941e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3142,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b7291ef17e418a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree3d752c1fee413e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6194,7 +6194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9db2bdfe27034f8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29b2e2e932134425"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re5c526ae30414228"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9331e8f1633e4806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R610a0aed92194aa4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R35557bf75fbb46ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7aefb821bb404f0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R616d47730b5a4ed6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rec6b97b2f76840b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R81f4ca35dfbf48c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
+        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
+        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1731,7 +1731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1a4a18e33e941e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1814dd26a5d7427f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3142,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree3d752c1fee413e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86133add317f459b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6194,7 +6194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29b2e2e932134425"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b1aeb3174114f8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7aefb821bb404f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R616d47730b5a4ed6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rec6b97b2f76840b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R81f4ca35dfbf48c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Re2f5cba08cd44483"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re1825ce45c1e447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rd571014def6d4de0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Reaec85d87e0c40ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-11-01T00:50:08.502Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>b59c831ec1c00c49183c1e83c86ee8d801e0152690935057f3be6f551a8b788b</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>2a343075b78e07a39b50033e252aeaec71194df376aa048789dba03e95d6e972</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1731,7 +1731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1814dd26a5d7427f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb84e8e650b8d49a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3142,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86133add317f459b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31acd3e3acfc4f26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6194,7 +6194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b1aeb3174114f8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fe94e42d95c41e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/distribution-controls/register.xlsx
+++ b/docs/electrical-grid/categories/distribution-controls/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7aefb821bb404f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R616d47730b5a4ed6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rec6b97b2f76840b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R81f4ca35dfbf48c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6a4b375ddffc47d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0728971194294899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R92b74f0fffcd46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R975f715c0cc84e86"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Distribution and controls. DB1, DB2, LC1, FC1 and AV1 enclosures, their shared supply feeders, and the socket-outlet circuits P1–P4. Model snapshot: 2026-11-01T01:42:20.339Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>50118e5af402ff0efaabf2d570ac3f0129d03efc89e10e7eeb51b8d67485750c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>0fb0ba42a427dbbe355fa325c0efcf0641bfb0dae62bd4f360bc65584cfd7d81</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1731,7 +1731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1814dd26a5d7427f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5eb6659cdd124b81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3142,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86133add317f459b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56845c9e663b4257"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6194,7 +6194,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b1aeb3174114f8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd71fde85d9f54354"/>
   </x:tableParts>
 </x:worksheet>
 </file>